--- a/backend/Tabelas.xlsx
+++ b/backend/Tabelas.xlsx
@@ -5,16 +5,17 @@
   <workbookPr defaultThemeVersion="166925"/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="https://d.docs.live.net/e1886f03fd9a8d1f/Desktop/Pasta Pessoal/Projeto App Pessoal/"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="https://d.docs.live.net/e1886f03fd9a8d1f/Desktop/Pasta Pessoal/Projeto App Pessoal/backend/"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="18" documentId="13_ncr:1_{13E58D98-281C-4A3C-A50A-D909604095A7}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{3C6277CB-6DDE-4E54-8966-E2B53BBCD58D}"/>
+  <xr:revisionPtr revIDLastSave="19" documentId="13_ncr:1_{13E58D98-281C-4A3C-A50A-D909604095A7}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{813AD361-0124-4A74-9422-741215A920A0}"/>
   <bookViews>
-    <workbookView xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="15840" activeTab="1" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="3960" yWindow="3660" windowWidth="21600" windowHeight="11385" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="Alimentos" sheetId="1" r:id="rId1"/>
-    <sheet name="Exercicios" sheetId="2" r:id="rId2"/>
+    <sheet name="Planilha1" sheetId="3" r:id="rId2"/>
+    <sheet name="Exercicios" sheetId="2" r:id="rId3"/>
   </sheets>
   <definedNames>
     <definedName name="_xlnm._FilterDatabase" localSheetId="0" hidden="1">Alimentos!$A$1:$G$591</definedName>
@@ -26,7 +27,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="861" uniqueCount="745">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="901" uniqueCount="778">
   <si>
     <t>id</t>
   </si>
@@ -2261,12 +2262,114 @@
   </si>
   <si>
     <t>Fator_Calorias</t>
+  </si>
+  <si>
+    <t>ID</t>
+  </si>
+  <si>
+    <t>V1</t>
+  </si>
+  <si>
+    <t>V2</t>
+  </si>
+  <si>
+    <t>V3</t>
+  </si>
+  <si>
+    <t>V4</t>
+  </si>
+  <si>
+    <t>V5</t>
+  </si>
+  <si>
+    <t>Caqui chocolate, cru</t>
+  </si>
+  <si>
+    <t>Laranja baía, crua</t>
+  </si>
+  <si>
+    <t>Laranja baía, suco</t>
+  </si>
+  <si>
+    <t>Laranja da terra, crua</t>
+  </si>
+  <si>
+    <t>Laranja da terra, suco</t>
+  </si>
+  <si>
+    <t>Laranja lima, crua</t>
+  </si>
+  <si>
+    <t>Laranja lima, suco</t>
+  </si>
+  <si>
+    <t>Laranja pêra, crua</t>
+  </si>
+  <si>
+    <t>Laranja pêra, suco</t>
+  </si>
+  <si>
+    <t>Laranja valência, crua</t>
+  </si>
+  <si>
+    <t>Laranja valência, suco</t>
+  </si>
+  <si>
+    <t>Maçã Argentina, crua</t>
+  </si>
+  <si>
+    <t>Maçã Fuji, crua</t>
+  </si>
+  <si>
+    <t>Mamão Formosa, cru</t>
+  </si>
+  <si>
+    <t>Mamão Papaia, cru</t>
+  </si>
+  <si>
+    <t>Manga Haden, crua</t>
+  </si>
+  <si>
+    <t>Manga Palmer, crua</t>
+  </si>
+  <si>
+    <t>Manga Tommy, crua</t>
+  </si>
+  <si>
+    <t>Ovo de codorna, cru</t>
+  </si>
+  <si>
+    <t>Ovo clara cozida</t>
+  </si>
+  <si>
+    <t>Ovo gema cozida</t>
+  </si>
+  <si>
+    <t>Ovo inteiro cozido</t>
+  </si>
+  <si>
+    <t>Ovo inteiro cru</t>
+  </si>
+  <si>
+    <t>Ovo inteiro frito</t>
+  </si>
+  <si>
+    <t>Pêssego Aurora, cru</t>
+  </si>
+  <si>
+    <t>Tangerina Poncã, crua</t>
+  </si>
+  <si>
+    <t>Tangerina Poncã, suco</t>
   </si>
 </sst>
 </file>
 
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:x16r2="http://schemas.microsoft.com/office/spreadsheetml/2015/02/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" mc:Ignorable="x14ac x16r2 xr">
+  <numFmts count="1">
+    <numFmt numFmtId="164" formatCode="0.000000"/>
+  </numFmts>
   <fonts count="2" x14ac:knownFonts="1">
     <font>
       <sz val="11"/>
@@ -2304,7 +2407,7 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="3">
+  <cellXfs count="4">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
@@ -2312,6 +2415,7 @@
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1">
       <alignment vertical="center" wrapText="1"/>
     </xf>
+    <xf numFmtId="164" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1"/>
   </cellXfs>
   <cellStyles count="1">
     <cellStyle name="Normal" xfId="0" builtinId="0"/>
@@ -2350,6 +2454,10 @@
 </file>
 
 <file path=xl/persons/person4.xml><?xml version="1.0" encoding="utf-8"?>
+<personList xmlns="http://schemas.microsoft.com/office/spreadsheetml/2018/threadedcomments" xmlns:x="http://schemas.openxmlformats.org/spreadsheetml/2006/main"/>
+</file>
+
+<file path=xl/persons/person5.xml><?xml version="1.0" encoding="utf-8"?>
 <personList xmlns="http://schemas.microsoft.com/office/spreadsheetml/2018/threadedcomments" xmlns:x="http://schemas.openxmlformats.org/spreadsheetml/2006/main"/>
 </file>
 
@@ -2663,6 +2771,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0000-000000000000}">
+  <sheetPr filterMode="1"/>
   <dimension ref="A1:G591"/>
   <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
   <cols>
@@ -2694,7 +2803,7 @@
         <v>610</v>
       </c>
     </row>
-    <row r="2" spans="1:7" x14ac:dyDescent="0.25">
+    <row r="2" spans="1:7" hidden="1" x14ac:dyDescent="0.25">
       <c r="A2">
         <v>1</v>
       </c>
@@ -2717,7 +2826,7 @@
         <v>2.7493333333333338E-2</v>
       </c>
     </row>
-    <row r="3" spans="1:7" x14ac:dyDescent="0.25">
+    <row r="3" spans="1:7" hidden="1" x14ac:dyDescent="0.25">
       <c r="A3">
         <v>2</v>
       </c>
@@ -2740,7 +2849,7 @@
         <v>4.819166666666666E-2</v>
       </c>
     </row>
-    <row r="4" spans="1:7" x14ac:dyDescent="0.25">
+    <row r="4" spans="1:7" hidden="1" x14ac:dyDescent="0.25">
       <c r="A4">
         <v>3</v>
       </c>
@@ -2763,7 +2872,7 @@
         <v>1.5609999999999999E-2</v>
       </c>
     </row>
-    <row r="5" spans="1:7" x14ac:dyDescent="0.25">
+    <row r="5" spans="1:7" hidden="1" x14ac:dyDescent="0.25">
       <c r="A5">
         <v>4</v>
       </c>
@@ -2786,7 +2895,7 @@
         <v>1.6391666666666665E-2</v>
       </c>
     </row>
-    <row r="6" spans="1:7" x14ac:dyDescent="0.25">
+    <row r="6" spans="1:7" hidden="1" x14ac:dyDescent="0.25">
       <c r="A6">
         <v>5</v>
       </c>
@@ -2809,7 +2918,7 @@
         <v>1.0696666666666665E-2</v>
       </c>
     </row>
-    <row r="7" spans="1:7" x14ac:dyDescent="0.25">
+    <row r="7" spans="1:7" hidden="1" x14ac:dyDescent="0.25">
       <c r="A7">
         <v>6</v>
       </c>
@@ -2832,7 +2941,7 @@
         <v>1.7198333333333333E-2</v>
       </c>
     </row>
-    <row r="8" spans="1:7" x14ac:dyDescent="0.25">
+    <row r="8" spans="1:7" hidden="1" x14ac:dyDescent="0.25">
       <c r="A8">
         <v>7</v>
       </c>
@@ -2855,7 +2964,7 @@
         <v>9.1300000000000006E-2</v>
       </c>
     </row>
-    <row r="9" spans="1:7" x14ac:dyDescent="0.25">
+    <row r="9" spans="1:7" hidden="1" x14ac:dyDescent="0.25">
       <c r="A9">
         <v>8</v>
       </c>
@@ -2878,7 +2987,7 @@
         <v>2.1000000000000001E-2</v>
       </c>
     </row>
-    <row r="10" spans="1:7" x14ac:dyDescent="0.25">
+    <row r="10" spans="1:7" hidden="1" x14ac:dyDescent="0.25">
       <c r="A10">
         <v>9</v>
       </c>
@@ -2901,7 +3010,7 @@
         <v>2.9566666666666672E-2</v>
       </c>
     </row>
-    <row r="11" spans="1:7" x14ac:dyDescent="0.25">
+    <row r="11" spans="1:7" hidden="1" x14ac:dyDescent="0.25">
       <c r="A11">
         <v>10</v>
       </c>
@@ -2924,7 +3033,7 @@
         <v>1.5333333333333332E-2</v>
       </c>
     </row>
-    <row r="12" spans="1:7" x14ac:dyDescent="0.25">
+    <row r="12" spans="1:7" hidden="1" x14ac:dyDescent="0.25">
       <c r="A12">
         <v>11</v>
       </c>
@@ -2947,7 +3056,7 @@
         <v>1.8033333333333335E-2</v>
       </c>
     </row>
-    <row r="13" spans="1:7" x14ac:dyDescent="0.25">
+    <row r="13" spans="1:7" hidden="1" x14ac:dyDescent="0.25">
       <c r="A13">
         <v>12</v>
       </c>
@@ -2970,7 +3079,7 @@
         <v>8.199999999999999E-3</v>
       </c>
     </row>
-    <row r="14" spans="1:7" x14ac:dyDescent="0.25">
+    <row r="14" spans="1:7" hidden="1" x14ac:dyDescent="0.25">
       <c r="A14">
         <v>13</v>
       </c>
@@ -2993,7 +3102,7 @@
         <v>2.5099999999999997E-2</v>
       </c>
     </row>
-    <row r="15" spans="1:7" x14ac:dyDescent="0.25">
+    <row r="15" spans="1:7" hidden="1" x14ac:dyDescent="0.25">
       <c r="A15">
         <v>14</v>
       </c>
@@ -3016,7 +3125,7 @@
         <v>1.7033333333333331E-2</v>
       </c>
     </row>
-    <row r="16" spans="1:7" x14ac:dyDescent="0.25">
+    <row r="16" spans="1:7" hidden="1" x14ac:dyDescent="0.25">
       <c r="A16">
         <v>15</v>
       </c>
@@ -3039,7 +3148,7 @@
         <v>6.9066666666666669E-3</v>
       </c>
     </row>
-    <row r="17" spans="1:7" x14ac:dyDescent="0.25">
+    <row r="17" spans="1:7" hidden="1" x14ac:dyDescent="0.25">
       <c r="A17">
         <v>16</v>
       </c>
@@ -3062,7 +3171,7 @@
         <v>1.43E-2</v>
       </c>
     </row>
-    <row r="18" spans="1:7" x14ac:dyDescent="0.25">
+    <row r="18" spans="1:7" hidden="1" x14ac:dyDescent="0.25">
       <c r="A18">
         <v>17</v>
       </c>
@@ -3085,7 +3194,7 @@
         <v>1.0549999999999999E-2</v>
       </c>
     </row>
-    <row r="19" spans="1:7" x14ac:dyDescent="0.25">
+    <row r="19" spans="1:7" hidden="1" x14ac:dyDescent="0.25">
       <c r="A19">
         <v>18</v>
       </c>
@@ -3108,7 +3217,7 @@
         <v>7.0999999999999995E-3</v>
       </c>
     </row>
-    <row r="20" spans="1:7" x14ac:dyDescent="0.25">
+    <row r="20" spans="1:7" hidden="1" x14ac:dyDescent="0.25">
       <c r="A20">
         <v>19</v>
       </c>
@@ -3131,7 +3240,7 @@
         <v>5.4993333333333332E-2</v>
       </c>
     </row>
-    <row r="21" spans="1:7" x14ac:dyDescent="0.25">
+    <row r="21" spans="1:7" hidden="1" x14ac:dyDescent="0.25">
       <c r="A21">
         <v>20</v>
       </c>
@@ -3154,7 +3263,7 @@
         <v>1.2166666666666666E-2</v>
       </c>
     </row>
-    <row r="22" spans="1:7" x14ac:dyDescent="0.25">
+    <row r="22" spans="1:7" hidden="1" x14ac:dyDescent="0.25">
       <c r="A22">
         <v>21</v>
       </c>
@@ -3177,7 +3286,7 @@
         <v>5.2933333333333332E-2</v>
       </c>
     </row>
-    <row r="23" spans="1:7" x14ac:dyDescent="0.25">
+    <row r="23" spans="1:7" hidden="1" x14ac:dyDescent="0.25">
       <c r="A23">
         <v>22</v>
       </c>
@@ -3200,7 +3309,7 @@
         <v>1.8366666666666667E-2</v>
       </c>
     </row>
-    <row r="24" spans="1:7" x14ac:dyDescent="0.25">
+    <row r="24" spans="1:7" hidden="1" x14ac:dyDescent="0.25">
       <c r="A24">
         <v>23</v>
       </c>
@@ -3223,7 +3332,7 @@
         <v>3.2133333333333333E-2</v>
       </c>
     </row>
-    <row r="25" spans="1:7" x14ac:dyDescent="0.25">
+    <row r="25" spans="1:7" hidden="1" x14ac:dyDescent="0.25">
       <c r="A25">
         <v>24</v>
       </c>
@@ -3246,7 +3355,7 @@
         <v>4.9833333333333334E-2</v>
       </c>
     </row>
-    <row r="26" spans="1:7" x14ac:dyDescent="0.25">
+    <row r="26" spans="1:7" hidden="1" x14ac:dyDescent="0.25">
       <c r="A26">
         <v>25</v>
       </c>
@@ -3269,7 +3378,7 @@
         <v>4.1166666666666664E-2</v>
       </c>
     </row>
-    <row r="27" spans="1:7" x14ac:dyDescent="0.25">
+    <row r="27" spans="1:7" hidden="1" x14ac:dyDescent="0.25">
       <c r="A27">
         <v>26</v>
       </c>
@@ -3292,7 +3401,7 @@
         <v>2.1066666666666668E-2</v>
       </c>
     </row>
-    <row r="28" spans="1:7" x14ac:dyDescent="0.25">
+    <row r="28" spans="1:7" hidden="1" x14ac:dyDescent="0.25">
       <c r="A28">
         <v>27</v>
       </c>
@@ -3315,7 +3424,7 @@
         <v>1.0713333333333332E-2</v>
       </c>
     </row>
-    <row r="29" spans="1:7" x14ac:dyDescent="0.25">
+    <row r="29" spans="1:7" hidden="1" x14ac:dyDescent="0.25">
       <c r="A29">
         <v>28</v>
       </c>
@@ -3338,7 +3447,7 @@
         <v>3.722333333333333E-2</v>
       </c>
     </row>
-    <row r="30" spans="1:7" x14ac:dyDescent="0.25">
+    <row r="30" spans="1:7" hidden="1" x14ac:dyDescent="0.25">
       <c r="A30">
         <v>29</v>
       </c>
@@ -3361,7 +3470,7 @@
         <v>4.5666666666666668E-3</v>
       </c>
     </row>
-    <row r="31" spans="1:7" x14ac:dyDescent="0.25">
+    <row r="31" spans="1:7" hidden="1" x14ac:dyDescent="0.25">
       <c r="A31">
         <v>30</v>
       </c>
@@ -3384,7 +3493,7 @@
         <v>2.5226666666666665E-2</v>
       </c>
     </row>
-    <row r="32" spans="1:7" x14ac:dyDescent="0.25">
+    <row r="32" spans="1:7" hidden="1" x14ac:dyDescent="0.25">
       <c r="A32">
         <v>31</v>
       </c>
@@ -3407,7 +3516,7 @@
         <v>5.7999999999999996E-3</v>
       </c>
     </row>
-    <row r="33" spans="1:7" x14ac:dyDescent="0.25">
+    <row r="33" spans="1:7" hidden="1" x14ac:dyDescent="0.25">
       <c r="A33">
         <v>32</v>
       </c>
@@ -3430,7 +3539,7 @@
         <v>0.15479999999999999</v>
       </c>
     </row>
-    <row r="34" spans="1:7" x14ac:dyDescent="0.25">
+    <row r="34" spans="1:7" hidden="1" x14ac:dyDescent="0.25">
       <c r="A34">
         <v>33</v>
       </c>
@@ -3453,7 +3562,7 @@
         <v>5.4900000000000004E-2</v>
       </c>
     </row>
-    <row r="35" spans="1:7" x14ac:dyDescent="0.25">
+    <row r="35" spans="1:7" hidden="1" x14ac:dyDescent="0.25">
       <c r="A35">
         <v>34</v>
       </c>
@@ -3476,7 +3585,7 @@
         <v>4.8233333333333329E-2</v>
       </c>
     </row>
-    <row r="36" spans="1:7" x14ac:dyDescent="0.25">
+    <row r="36" spans="1:7" hidden="1" x14ac:dyDescent="0.25">
       <c r="A36">
         <v>35</v>
       </c>
@@ -3499,7 +3608,7 @@
         <v>2.3466666666666667E-2</v>
       </c>
     </row>
-    <row r="37" spans="1:7" x14ac:dyDescent="0.25">
+    <row r="37" spans="1:7" hidden="1" x14ac:dyDescent="0.25">
       <c r="A37">
         <v>36</v>
       </c>
@@ -3522,7 +3631,7 @@
         <v>1.9400000000000001E-2</v>
       </c>
     </row>
-    <row r="38" spans="1:7" x14ac:dyDescent="0.25">
+    <row r="38" spans="1:7" hidden="1" x14ac:dyDescent="0.25">
       <c r="A38">
         <v>37</v>
       </c>
@@ -3545,7 +3654,7 @@
         <v>1.636333333333333E-2</v>
       </c>
     </row>
-    <row r="39" spans="1:7" x14ac:dyDescent="0.25">
+    <row r="39" spans="1:7" hidden="1" x14ac:dyDescent="0.25">
       <c r="A39">
         <v>38</v>
       </c>
@@ -3568,7 +3677,7 @@
         <v>1.6063333333333332E-2</v>
       </c>
     </row>
-    <row r="40" spans="1:7" x14ac:dyDescent="0.25">
+    <row r="40" spans="1:7" hidden="1" x14ac:dyDescent="0.25">
       <c r="A40">
         <v>39</v>
       </c>
@@ -3591,7 +3700,7 @@
         <v>5.6100000000000004E-2</v>
       </c>
     </row>
-    <row r="41" spans="1:7" x14ac:dyDescent="0.25">
+    <row r="41" spans="1:7" hidden="1" x14ac:dyDescent="0.25">
       <c r="A41">
         <v>40</v>
       </c>
@@ -3614,7 +3723,7 @@
         <v>2.9266666666666663E-2</v>
       </c>
     </row>
-    <row r="42" spans="1:7" x14ac:dyDescent="0.25">
+    <row r="42" spans="1:7" hidden="1" x14ac:dyDescent="0.25">
       <c r="A42">
         <v>41</v>
       </c>
@@ -3637,7 +3746,7 @@
         <v>2.2966666666666663E-2</v>
       </c>
     </row>
-    <row r="43" spans="1:7" x14ac:dyDescent="0.25">
+    <row r="43" spans="1:7" hidden="1" x14ac:dyDescent="0.25">
       <c r="A43">
         <v>42</v>
       </c>
@@ -3660,7 +3769,7 @@
         <v>7.4333329999999994E-3</v>
       </c>
     </row>
-    <row r="44" spans="1:7" x14ac:dyDescent="0.25">
+    <row r="44" spans="1:7" hidden="1" x14ac:dyDescent="0.25">
       <c r="A44">
         <v>43</v>
       </c>
@@ -3683,7 +3792,7 @@
         <v>4.713333333333334E-2</v>
       </c>
     </row>
-    <row r="45" spans="1:7" x14ac:dyDescent="0.25">
+    <row r="45" spans="1:7" hidden="1" x14ac:dyDescent="0.25">
       <c r="A45">
         <v>44</v>
       </c>
@@ -3706,7 +3815,7 @@
         <v>3.9180000000000006E-2</v>
       </c>
     </row>
-    <row r="46" spans="1:7" x14ac:dyDescent="0.25">
+    <row r="46" spans="1:7" hidden="1" x14ac:dyDescent="0.25">
       <c r="A46">
         <v>45</v>
       </c>
@@ -3729,7 +3838,7 @@
         <v>4.6433333333333333E-2</v>
       </c>
     </row>
-    <row r="47" spans="1:7" x14ac:dyDescent="0.25">
+    <row r="47" spans="1:7" hidden="1" x14ac:dyDescent="0.25">
       <c r="A47">
         <v>46</v>
       </c>
@@ -3752,7 +3861,7 @@
         <v>8.8000000000000005E-3</v>
       </c>
     </row>
-    <row r="48" spans="1:7" x14ac:dyDescent="0.25">
+    <row r="48" spans="1:7" hidden="1" x14ac:dyDescent="0.25">
       <c r="A48">
         <v>47</v>
       </c>
@@ -3775,7 +3884,7 @@
         <v>2.3709999999999998E-2</v>
       </c>
     </row>
-    <row r="49" spans="1:7" x14ac:dyDescent="0.25">
+    <row r="49" spans="1:7" hidden="1" x14ac:dyDescent="0.25">
       <c r="A49">
         <v>48</v>
       </c>
@@ -3798,7 +3907,7 @@
         <v>5.9800000000000006E-2</v>
       </c>
     </row>
-    <row r="50" spans="1:7" x14ac:dyDescent="0.25">
+    <row r="50" spans="1:7" hidden="1" x14ac:dyDescent="0.25">
       <c r="A50">
         <v>49</v>
       </c>
@@ -3821,7 +3930,7 @@
         <v>5.7066666666666668E-2</v>
       </c>
     </row>
-    <row r="51" spans="1:7" x14ac:dyDescent="0.25">
+    <row r="51" spans="1:7" hidden="1" x14ac:dyDescent="0.25">
       <c r="A51">
         <v>50</v>
       </c>
@@ -3844,7 +3953,7 @@
         <v>2.4799999999999999E-2</v>
       </c>
     </row>
-    <row r="52" spans="1:7" x14ac:dyDescent="0.25">
+    <row r="52" spans="1:7" hidden="1" x14ac:dyDescent="0.25">
       <c r="A52">
         <v>51</v>
       </c>
@@ -3867,7 +3976,7 @@
         <v>4.296666666666666E-2</v>
       </c>
     </row>
-    <row r="53" spans="1:7" x14ac:dyDescent="0.25">
+    <row r="53" spans="1:7" hidden="1" x14ac:dyDescent="0.25">
       <c r="A53">
         <v>52</v>
       </c>
@@ -3890,7 +3999,7 @@
         <v>6.883333333333333E-2</v>
       </c>
     </row>
-    <row r="54" spans="1:7" x14ac:dyDescent="0.25">
+    <row r="54" spans="1:7" hidden="1" x14ac:dyDescent="0.25">
       <c r="A54">
         <v>53</v>
       </c>
@@ -3913,7 +4022,7 @@
         <v>2.3066666666666666E-2</v>
       </c>
     </row>
-    <row r="55" spans="1:7" x14ac:dyDescent="0.25">
+    <row r="55" spans="1:7" hidden="1" x14ac:dyDescent="0.25">
       <c r="A55">
         <v>54</v>
       </c>
@@ -3936,7 +4045,7 @@
         <v>2.4333333333333332E-2</v>
       </c>
     </row>
-    <row r="56" spans="1:7" x14ac:dyDescent="0.25">
+    <row r="56" spans="1:7" hidden="1" x14ac:dyDescent="0.25">
       <c r="A56">
         <v>55</v>
       </c>
@@ -3959,7 +4068,7 @@
         <v>1.04E-2</v>
       </c>
     </row>
-    <row r="57" spans="1:7" x14ac:dyDescent="0.25">
+    <row r="57" spans="1:7" hidden="1" x14ac:dyDescent="0.25">
       <c r="A57">
         <v>56</v>
       </c>
@@ -3982,7 +4091,7 @@
         <v>9.8666666666666677E-3</v>
       </c>
     </row>
-    <row r="58" spans="1:7" x14ac:dyDescent="0.25">
+    <row r="58" spans="1:7" hidden="1" x14ac:dyDescent="0.25">
       <c r="A58">
         <v>57</v>
       </c>
@@ -4005,7 +4114,7 @@
         <v>1.1066666666666667E-2</v>
       </c>
     </row>
-    <row r="59" spans="1:7" x14ac:dyDescent="0.25">
+    <row r="59" spans="1:7" hidden="1" x14ac:dyDescent="0.25">
       <c r="A59">
         <v>58</v>
       </c>
@@ -4028,7 +4137,7 @@
         <v>9.4333333333333335E-3</v>
       </c>
     </row>
-    <row r="60" spans="1:7" x14ac:dyDescent="0.25">
+    <row r="60" spans="1:7" hidden="1" x14ac:dyDescent="0.25">
       <c r="A60">
         <v>59</v>
       </c>
@@ -4051,7 +4160,7 @@
         <v>1.4133333333333333E-2</v>
       </c>
     </row>
-    <row r="61" spans="1:7" x14ac:dyDescent="0.25">
+    <row r="61" spans="1:7" hidden="1" x14ac:dyDescent="0.25">
       <c r="A61">
         <v>60</v>
       </c>
@@ -4074,7 +4183,7 @@
         <v>1.3093333333333332E-2</v>
       </c>
     </row>
-    <row r="62" spans="1:7" x14ac:dyDescent="0.25">
+    <row r="62" spans="1:7" hidden="1" x14ac:dyDescent="0.25">
       <c r="A62">
         <v>61</v>
       </c>
@@ -4097,7 +4206,7 @@
         <v>0.14336666666666667</v>
       </c>
     </row>
-    <row r="63" spans="1:7" x14ac:dyDescent="0.25">
+    <row r="63" spans="1:7" hidden="1" x14ac:dyDescent="0.25">
       <c r="A63">
         <v>62</v>
       </c>
@@ -4120,7 +4229,7 @@
         <v>2.4033333333333334E-2</v>
       </c>
     </row>
-    <row r="64" spans="1:7" x14ac:dyDescent="0.25">
+    <row r="64" spans="1:7" hidden="1" x14ac:dyDescent="0.25">
       <c r="A64">
         <v>63</v>
       </c>
@@ -4143,7 +4252,7 @@
         <v>3.3950000000000001E-2</v>
       </c>
     </row>
-    <row r="65" spans="1:7" x14ac:dyDescent="0.25">
+    <row r="65" spans="1:7" hidden="1" x14ac:dyDescent="0.25">
       <c r="A65">
         <v>64</v>
       </c>
@@ -4166,7 +4275,7 @@
         <v>1.2333333333333332E-2</v>
       </c>
     </row>
-    <row r="66" spans="1:7" x14ac:dyDescent="0.25">
+    <row r="66" spans="1:7" hidden="1" x14ac:dyDescent="0.25">
       <c r="A66">
         <v>65</v>
       </c>
@@ -4212,7 +4321,7 @@
         <v>6.3133333333333319E-2</v>
       </c>
     </row>
-    <row r="68" spans="1:7" x14ac:dyDescent="0.25">
+    <row r="68" spans="1:7" hidden="1" x14ac:dyDescent="0.25">
       <c r="A68">
         <v>67</v>
       </c>
@@ -4235,7 +4344,7 @@
         <v>9.8666666666666677E-3</v>
       </c>
     </row>
-    <row r="69" spans="1:7" x14ac:dyDescent="0.25">
+    <row r="69" spans="1:7" hidden="1" x14ac:dyDescent="0.25">
       <c r="A69">
         <v>68</v>
       </c>
@@ -4258,7 +4367,7 @@
         <v>3.2666666666666664E-3</v>
       </c>
     </row>
-    <row r="70" spans="1:7" x14ac:dyDescent="0.25">
+    <row r="70" spans="1:7" hidden="1" x14ac:dyDescent="0.25">
       <c r="A70">
         <v>69</v>
       </c>
@@ -4281,7 +4390,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="71" spans="1:7" x14ac:dyDescent="0.25">
+    <row r="71" spans="1:7" hidden="1" x14ac:dyDescent="0.25">
       <c r="A71">
         <v>70</v>
       </c>
@@ -4304,7 +4413,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="72" spans="1:7" x14ac:dyDescent="0.25">
+    <row r="72" spans="1:7" hidden="1" x14ac:dyDescent="0.25">
       <c r="A72">
         <v>71</v>
       </c>
@@ -4327,7 +4436,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="73" spans="1:7" x14ac:dyDescent="0.25">
+    <row r="73" spans="1:7" hidden="1" x14ac:dyDescent="0.25">
       <c r="A73">
         <v>72</v>
       </c>
@@ -4350,7 +4459,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="74" spans="1:7" x14ac:dyDescent="0.25">
+    <row r="74" spans="1:7" hidden="1" x14ac:dyDescent="0.25">
       <c r="A74">
         <v>73</v>
       </c>
@@ -4373,7 +4482,7 @@
         <v>1.6959999999999999E-2</v>
       </c>
     </row>
-    <row r="75" spans="1:7" x14ac:dyDescent="0.25">
+    <row r="75" spans="1:7" hidden="1" x14ac:dyDescent="0.25">
       <c r="A75">
         <v>74</v>
       </c>
@@ -4396,7 +4505,7 @@
         <v>2.4626666666666668E-2</v>
       </c>
     </row>
-    <row r="76" spans="1:7" x14ac:dyDescent="0.25">
+    <row r="76" spans="1:7" hidden="1" x14ac:dyDescent="0.25">
       <c r="A76">
         <v>75</v>
       </c>
@@ -4419,7 +4528,7 @@
         <v>2.1666666666666664E-2</v>
       </c>
     </row>
-    <row r="77" spans="1:7" x14ac:dyDescent="0.25">
+    <row r="77" spans="1:7" hidden="1" x14ac:dyDescent="0.25">
       <c r="A77">
         <v>76</v>
       </c>
@@ -4442,7 +4551,7 @@
         <v>1.1699999999999999E-2</v>
       </c>
     </row>
-    <row r="78" spans="1:7" x14ac:dyDescent="0.25">
+    <row r="78" spans="1:7" hidden="1" x14ac:dyDescent="0.25">
       <c r="A78">
         <v>77</v>
       </c>
@@ -4465,7 +4574,7 @@
         <v>1.7033333333333331E-2</v>
       </c>
     </row>
-    <row r="79" spans="1:7" x14ac:dyDescent="0.25">
+    <row r="79" spans="1:7" hidden="1" x14ac:dyDescent="0.25">
       <c r="A79">
         <v>78</v>
       </c>
@@ -4488,7 +4597,7 @@
         <v>1.5466666666666668E-2</v>
       </c>
     </row>
-    <row r="80" spans="1:7" x14ac:dyDescent="0.25">
+    <row r="80" spans="1:7" hidden="1" x14ac:dyDescent="0.25">
       <c r="A80">
         <v>79</v>
       </c>
@@ -4511,7 +4620,7 @@
         <v>2.300333333333333E-2</v>
       </c>
     </row>
-    <row r="81" spans="1:7" x14ac:dyDescent="0.25">
+    <row r="81" spans="1:7" hidden="1" x14ac:dyDescent="0.25">
       <c r="A81">
         <v>80</v>
       </c>
@@ -4534,7 +4643,7 @@
         <v>1.5880000000000002E-2</v>
       </c>
     </row>
-    <row r="82" spans="1:7" x14ac:dyDescent="0.25">
+    <row r="82" spans="1:7" hidden="1" x14ac:dyDescent="0.25">
       <c r="A82">
         <v>81</v>
       </c>
@@ -4557,7 +4666,7 @@
         <v>1.3533333333333335E-2</v>
       </c>
     </row>
-    <row r="83" spans="1:7" x14ac:dyDescent="0.25">
+    <row r="83" spans="1:7" hidden="1" x14ac:dyDescent="0.25">
       <c r="A83">
         <v>82</v>
       </c>
@@ -4580,7 +4689,7 @@
         <v>1.38E-2</v>
       </c>
     </row>
-    <row r="84" spans="1:7" x14ac:dyDescent="0.25">
+    <row r="84" spans="1:7" hidden="1" x14ac:dyDescent="0.25">
       <c r="A84">
         <v>83</v>
       </c>
@@ -4603,7 +4712,7 @@
         <v>2.605E-2</v>
       </c>
     </row>
-    <row r="85" spans="1:7" x14ac:dyDescent="0.25">
+    <row r="85" spans="1:7" hidden="1" x14ac:dyDescent="0.25">
       <c r="A85">
         <v>84</v>
       </c>
@@ -4626,7 +4735,7 @@
         <v>1.7233333333333333E-2</v>
       </c>
     </row>
-    <row r="86" spans="1:7" x14ac:dyDescent="0.25">
+    <row r="86" spans="1:7" hidden="1" x14ac:dyDescent="0.25">
       <c r="A86">
         <v>85</v>
       </c>
@@ -4649,7 +4758,7 @@
         <v>2.5533333333333331E-2</v>
       </c>
     </row>
-    <row r="87" spans="1:7" x14ac:dyDescent="0.25">
+    <row r="87" spans="1:7" hidden="1" x14ac:dyDescent="0.25">
       <c r="A87">
         <v>86</v>
       </c>
@@ -4672,7 +4781,7 @@
         <v>9.3583333333333324E-2</v>
       </c>
     </row>
-    <row r="88" spans="1:7" x14ac:dyDescent="0.25">
+    <row r="88" spans="1:7" hidden="1" x14ac:dyDescent="0.25">
       <c r="A88">
         <v>87</v>
       </c>
@@ -4695,7 +4804,7 @@
         <v>1.1220000000000001E-2</v>
       </c>
     </row>
-    <row r="89" spans="1:7" x14ac:dyDescent="0.25">
+    <row r="89" spans="1:7" hidden="1" x14ac:dyDescent="0.25">
       <c r="A89">
         <v>88</v>
       </c>
@@ -4718,7 +4827,7 @@
         <v>1.5113333333333333E-2</v>
       </c>
     </row>
-    <row r="90" spans="1:7" x14ac:dyDescent="0.25">
+    <row r="90" spans="1:7" hidden="1" x14ac:dyDescent="0.25">
       <c r="A90">
         <v>89</v>
       </c>
@@ -4741,7 +4850,7 @@
         <v>7.0333333333333324E-3</v>
       </c>
     </row>
-    <row r="91" spans="1:7" x14ac:dyDescent="0.25">
+    <row r="91" spans="1:7" hidden="1" x14ac:dyDescent="0.25">
       <c r="A91">
         <v>90</v>
       </c>
@@ -4764,7 +4873,7 @@
         <v>3.8900000000000004E-2</v>
       </c>
     </row>
-    <row r="92" spans="1:7" x14ac:dyDescent="0.25">
+    <row r="92" spans="1:7" hidden="1" x14ac:dyDescent="0.25">
       <c r="A92">
         <v>91</v>
       </c>
@@ -4787,7 +4896,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="93" spans="1:7" x14ac:dyDescent="0.25">
+    <row r="93" spans="1:7" hidden="1" x14ac:dyDescent="0.25">
       <c r="A93">
         <v>92</v>
       </c>
@@ -4810,7 +4919,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="94" spans="1:7" x14ac:dyDescent="0.25">
+    <row r="94" spans="1:7" hidden="1" x14ac:dyDescent="0.25">
       <c r="A94">
         <v>93</v>
       </c>
@@ -4833,7 +4942,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="95" spans="1:7" x14ac:dyDescent="0.25">
+    <row r="95" spans="1:7" hidden="1" x14ac:dyDescent="0.25">
       <c r="A95">
         <v>94</v>
       </c>
@@ -4856,7 +4965,7 @@
         <v>2.1366666666666666E-2</v>
       </c>
     </row>
-    <row r="96" spans="1:7" x14ac:dyDescent="0.25">
+    <row r="96" spans="1:7" hidden="1" x14ac:dyDescent="0.25">
       <c r="A96">
         <v>95</v>
       </c>
@@ -4879,7 +4988,7 @@
         <v>9.5699999999999986E-3</v>
       </c>
     </row>
-    <row r="97" spans="1:7" x14ac:dyDescent="0.25">
+    <row r="97" spans="1:7" hidden="1" x14ac:dyDescent="0.25">
       <c r="A97">
         <v>96</v>
       </c>
@@ -4902,7 +5011,7 @@
         <v>1.0216666666666667E-2</v>
       </c>
     </row>
-    <row r="98" spans="1:7" x14ac:dyDescent="0.25">
+    <row r="98" spans="1:7" hidden="1" x14ac:dyDescent="0.25">
       <c r="A98">
         <v>97</v>
       </c>
@@ -4925,7 +5034,7 @@
         <v>1.8266666666666667E-2</v>
       </c>
     </row>
-    <row r="99" spans="1:7" x14ac:dyDescent="0.25">
+    <row r="99" spans="1:7" hidden="1" x14ac:dyDescent="0.25">
       <c r="A99">
         <v>98</v>
       </c>
@@ -4948,7 +5057,7 @@
         <v>2.3300000000000001E-2</v>
       </c>
     </row>
-    <row r="100" spans="1:7" x14ac:dyDescent="0.25">
+    <row r="100" spans="1:7" hidden="1" x14ac:dyDescent="0.25">
       <c r="A100">
         <v>99</v>
       </c>
@@ -4971,7 +5080,7 @@
         <v>2.0133333333333333E-2</v>
       </c>
     </row>
-    <row r="101" spans="1:7" x14ac:dyDescent="0.25">
+    <row r="101" spans="1:7" hidden="1" x14ac:dyDescent="0.25">
       <c r="A101">
         <v>100</v>
       </c>
@@ -4994,7 +5103,7 @@
         <v>4.1403333333333334E-2</v>
       </c>
     </row>
-    <row r="102" spans="1:7" x14ac:dyDescent="0.25">
+    <row r="102" spans="1:7" hidden="1" x14ac:dyDescent="0.25">
       <c r="A102">
         <v>101</v>
       </c>
@@ -5017,7 +5126,7 @@
         <v>4.3233333333333332E-2</v>
       </c>
     </row>
-    <row r="103" spans="1:7" x14ac:dyDescent="0.25">
+    <row r="103" spans="1:7" hidden="1" x14ac:dyDescent="0.25">
       <c r="A103">
         <v>102</v>
       </c>
@@ -5040,7 +5149,7 @@
         <v>2.5066666666666668E-2</v>
       </c>
     </row>
-    <row r="104" spans="1:7" x14ac:dyDescent="0.25">
+    <row r="104" spans="1:7" hidden="1" x14ac:dyDescent="0.25">
       <c r="A104">
         <v>103</v>
       </c>
@@ -5063,7 +5172,7 @@
         <v>2.586666666666667E-2</v>
       </c>
     </row>
-    <row r="105" spans="1:7" x14ac:dyDescent="0.25">
+    <row r="105" spans="1:7" hidden="1" x14ac:dyDescent="0.25">
       <c r="A105">
         <v>104</v>
       </c>
@@ -5086,7 +5195,7 @@
         <v>3.4276666666666664E-2</v>
       </c>
     </row>
-    <row r="106" spans="1:7" x14ac:dyDescent="0.25">
+    <row r="106" spans="1:7" hidden="1" x14ac:dyDescent="0.25">
       <c r="A106">
         <v>105</v>
       </c>
@@ -5132,7 +5241,7 @@
         <v>2.4333333333333332E-2</v>
       </c>
     </row>
-    <row r="108" spans="1:7" x14ac:dyDescent="0.25">
+    <row r="108" spans="1:7" hidden="1" x14ac:dyDescent="0.25">
       <c r="A108">
         <v>107</v>
       </c>
@@ -5155,7 +5264,7 @@
         <v>4.5466666666666669E-2</v>
       </c>
     </row>
-    <row r="109" spans="1:7" x14ac:dyDescent="0.25">
+    <row r="109" spans="1:7" hidden="1" x14ac:dyDescent="0.25">
       <c r="A109">
         <v>108</v>
       </c>
@@ -5178,7 +5287,7 @@
         <v>0.1164</v>
       </c>
     </row>
-    <row r="110" spans="1:7" x14ac:dyDescent="0.25">
+    <row r="110" spans="1:7" hidden="1" x14ac:dyDescent="0.25">
       <c r="A110">
         <v>109</v>
       </c>
@@ -5201,7 +5310,7 @@
         <v>8.0360000000000001E-2</v>
       </c>
     </row>
-    <row r="111" spans="1:7" x14ac:dyDescent="0.25">
+    <row r="111" spans="1:7" hidden="1" x14ac:dyDescent="0.25">
       <c r="A111">
         <v>110</v>
       </c>
@@ -5224,7 +5333,7 @@
         <v>7.7633333333333332E-2</v>
       </c>
     </row>
-    <row r="112" spans="1:7" x14ac:dyDescent="0.25">
+    <row r="112" spans="1:7" hidden="1" x14ac:dyDescent="0.25">
       <c r="A112">
         <v>111</v>
       </c>
@@ -5247,7 +5356,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="113" spans="1:7" x14ac:dyDescent="0.25">
+    <row r="113" spans="1:7" hidden="1" x14ac:dyDescent="0.25">
       <c r="A113">
         <v>112</v>
       </c>
@@ -5270,7 +5379,7 @@
         <v>1.5016666666666669E-2</v>
       </c>
     </row>
-    <row r="114" spans="1:7" x14ac:dyDescent="0.25">
+    <row r="114" spans="1:7" hidden="1" x14ac:dyDescent="0.25">
       <c r="A114">
         <v>113</v>
       </c>
@@ -5293,7 +5402,7 @@
         <v>2.1353333333333335E-2</v>
       </c>
     </row>
-    <row r="115" spans="1:7" x14ac:dyDescent="0.25">
+    <row r="115" spans="1:7" hidden="1" x14ac:dyDescent="0.25">
       <c r="A115">
         <v>114</v>
       </c>
@@ -5316,7 +5425,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="116" spans="1:7" x14ac:dyDescent="0.25">
+    <row r="116" spans="1:7" hidden="1" x14ac:dyDescent="0.25">
       <c r="A116">
         <v>115</v>
       </c>
@@ -5339,7 +5448,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="117" spans="1:7" x14ac:dyDescent="0.25">
+    <row r="117" spans="1:7" hidden="1" x14ac:dyDescent="0.25">
       <c r="A117">
         <v>116</v>
       </c>
@@ -5362,7 +5471,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="118" spans="1:7" x14ac:dyDescent="0.25">
+    <row r="118" spans="1:7" hidden="1" x14ac:dyDescent="0.25">
       <c r="A118">
         <v>117</v>
       </c>
@@ -5385,7 +5494,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="119" spans="1:7" x14ac:dyDescent="0.25">
+    <row r="119" spans="1:7" hidden="1" x14ac:dyDescent="0.25">
       <c r="A119">
         <v>118</v>
       </c>
@@ -5408,7 +5517,7 @@
         <v>4.555E-2</v>
       </c>
     </row>
-    <row r="120" spans="1:7" x14ac:dyDescent="0.25">
+    <row r="120" spans="1:7" hidden="1" x14ac:dyDescent="0.25">
       <c r="A120">
         <v>119</v>
       </c>
@@ -5431,7 +5540,7 @@
         <v>3.8456666666666667E-2</v>
       </c>
     </row>
-    <row r="121" spans="1:7" x14ac:dyDescent="0.25">
+    <row r="121" spans="1:7" hidden="1" x14ac:dyDescent="0.25">
       <c r="A121">
         <v>120</v>
       </c>
@@ -5454,7 +5563,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="122" spans="1:7" x14ac:dyDescent="0.25">
+    <row r="122" spans="1:7" hidden="1" x14ac:dyDescent="0.25">
       <c r="A122">
         <v>121</v>
       </c>
@@ -5477,7 +5586,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="123" spans="1:7" x14ac:dyDescent="0.25">
+    <row r="123" spans="1:7" hidden="1" x14ac:dyDescent="0.25">
       <c r="A123">
         <v>122</v>
       </c>
@@ -5684,7 +5793,7 @@
         <v>2.0433333333333335E-2</v>
       </c>
     </row>
-    <row r="132" spans="1:7" x14ac:dyDescent="0.25">
+    <row r="132" spans="1:7" hidden="1" x14ac:dyDescent="0.25">
       <c r="A132">
         <v>131</v>
       </c>
@@ -5707,7 +5816,7 @@
         <v>1.4666666666666669E-3</v>
       </c>
     </row>
-    <row r="133" spans="1:7" x14ac:dyDescent="0.25">
+    <row r="133" spans="1:7" hidden="1" x14ac:dyDescent="0.25">
       <c r="A133">
         <v>132</v>
       </c>
@@ -5730,7 +5839,7 @@
         <v>1.7579999999999998E-2</v>
       </c>
     </row>
-    <row r="134" spans="1:7" x14ac:dyDescent="0.25">
+    <row r="134" spans="1:7" hidden="1" x14ac:dyDescent="0.25">
       <c r="A134">
         <v>133</v>
       </c>
@@ -5753,7 +5862,7 @@
         <v>2.063333333333333E-2</v>
       </c>
     </row>
-    <row r="135" spans="1:7" x14ac:dyDescent="0.25">
+    <row r="135" spans="1:7" hidden="1" x14ac:dyDescent="0.25">
       <c r="A135">
         <v>134</v>
       </c>
@@ -5776,7 +5885,7 @@
         <v>2.2120000000000001E-2</v>
       </c>
     </row>
-    <row r="136" spans="1:7" x14ac:dyDescent="0.25">
+    <row r="136" spans="1:7" hidden="1" x14ac:dyDescent="0.25">
       <c r="A136">
         <v>135</v>
       </c>
@@ -5799,7 +5908,7 @@
         <v>2.5733333333333327E-2</v>
       </c>
     </row>
-    <row r="137" spans="1:7" x14ac:dyDescent="0.25">
+    <row r="137" spans="1:7" hidden="1" x14ac:dyDescent="0.25">
       <c r="A137">
         <v>136</v>
       </c>
@@ -5822,7 +5931,7 @@
         <v>2.4556666666666668E-2</v>
       </c>
     </row>
-    <row r="138" spans="1:7" x14ac:dyDescent="0.25">
+    <row r="138" spans="1:7" hidden="1" x14ac:dyDescent="0.25">
       <c r="A138">
         <v>137</v>
       </c>
@@ -5845,7 +5954,7 @@
         <v>1.3433333333333335E-2</v>
       </c>
     </row>
-    <row r="139" spans="1:7" x14ac:dyDescent="0.25">
+    <row r="139" spans="1:7" hidden="1" x14ac:dyDescent="0.25">
       <c r="A139">
         <v>138</v>
       </c>
@@ -5868,7 +5977,7 @@
         <v>1.1633333333333334E-2</v>
       </c>
     </row>
-    <row r="140" spans="1:7" x14ac:dyDescent="0.25">
+    <row r="140" spans="1:7" hidden="1" x14ac:dyDescent="0.25">
       <c r="A140">
         <v>139</v>
       </c>
@@ -5891,7 +6000,7 @@
         <v>8.0593333333333336E-2</v>
       </c>
     </row>
-    <row r="141" spans="1:7" x14ac:dyDescent="0.25">
+    <row r="141" spans="1:7" hidden="1" x14ac:dyDescent="0.25">
       <c r="A141">
         <v>140</v>
       </c>
@@ -5914,7 +6023,7 @@
         <v>1.3769999999999999E-2</v>
       </c>
     </row>
-    <row r="142" spans="1:7" x14ac:dyDescent="0.25">
+    <row r="142" spans="1:7" hidden="1" x14ac:dyDescent="0.25">
       <c r="A142">
         <v>141</v>
       </c>
@@ -5937,7 +6046,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="143" spans="1:7" x14ac:dyDescent="0.25">
+    <row r="143" spans="1:7" hidden="1" x14ac:dyDescent="0.25">
       <c r="A143">
         <v>142</v>
       </c>
@@ -5960,7 +6069,7 @@
         <v>2.9333333333333338E-3</v>
       </c>
     </row>
-    <row r="144" spans="1:7" x14ac:dyDescent="0.25">
+    <row r="144" spans="1:7" hidden="1" x14ac:dyDescent="0.25">
       <c r="A144">
         <v>143</v>
       </c>
@@ -5983,7 +6092,7 @@
         <v>2.5243333333333333E-2</v>
       </c>
     </row>
-    <row r="145" spans="1:7" x14ac:dyDescent="0.25">
+    <row r="145" spans="1:7" hidden="1" x14ac:dyDescent="0.25">
       <c r="A145">
         <v>144</v>
       </c>
@@ -6006,7 +6115,7 @@
         <v>2.8733333333333329E-2</v>
       </c>
     </row>
-    <row r="146" spans="1:7" x14ac:dyDescent="0.25">
+    <row r="146" spans="1:7" hidden="1" x14ac:dyDescent="0.25">
       <c r="A146">
         <v>145</v>
       </c>
@@ -6029,7 +6138,7 @@
         <v>1.8786666666666663E-2</v>
       </c>
     </row>
-    <row r="147" spans="1:7" x14ac:dyDescent="0.25">
+    <row r="147" spans="1:7" hidden="1" x14ac:dyDescent="0.25">
       <c r="A147">
         <v>146</v>
       </c>
@@ -6052,7 +6161,7 @@
         <v>3.3733333333333337E-2</v>
       </c>
     </row>
-    <row r="148" spans="1:7" x14ac:dyDescent="0.25">
+    <row r="148" spans="1:7" hidden="1" x14ac:dyDescent="0.25">
       <c r="A148">
         <v>147</v>
       </c>
@@ -6075,7 +6184,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="149" spans="1:7" x14ac:dyDescent="0.25">
+    <row r="149" spans="1:7" hidden="1" x14ac:dyDescent="0.25">
       <c r="A149">
         <v>148</v>
       </c>
@@ -6098,7 +6207,7 @@
         <v>1.159E-2</v>
       </c>
     </row>
-    <row r="150" spans="1:7" x14ac:dyDescent="0.25">
+    <row r="150" spans="1:7" hidden="1" x14ac:dyDescent="0.25">
       <c r="A150">
         <v>149</v>
       </c>
@@ -6121,7 +6230,7 @@
         <v>2.7373333333333333E-2</v>
       </c>
     </row>
-    <row r="151" spans="1:7" x14ac:dyDescent="0.25">
+    <row r="151" spans="1:7" hidden="1" x14ac:dyDescent="0.25">
       <c r="A151">
         <v>150</v>
       </c>
@@ -6144,7 +6253,7 @@
         <v>3.4166666666666665E-2</v>
       </c>
     </row>
-    <row r="152" spans="1:7" x14ac:dyDescent="0.25">
+    <row r="152" spans="1:7" hidden="1" x14ac:dyDescent="0.25">
       <c r="A152">
         <v>151</v>
       </c>
@@ -6167,7 +6276,7 @@
         <v>2.8799999999999999E-2</v>
       </c>
     </row>
-    <row r="153" spans="1:7" x14ac:dyDescent="0.25">
+    <row r="153" spans="1:7" hidden="1" x14ac:dyDescent="0.25">
       <c r="A153">
         <v>152</v>
       </c>
@@ -6190,7 +6299,7 @@
         <v>5.3666666666666672E-3</v>
       </c>
     </row>
-    <row r="154" spans="1:7" x14ac:dyDescent="0.25">
+    <row r="154" spans="1:7" hidden="1" x14ac:dyDescent="0.25">
       <c r="A154">
         <v>153</v>
       </c>
@@ -6213,7 +6322,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="155" spans="1:7" x14ac:dyDescent="0.25">
+    <row r="155" spans="1:7" hidden="1" x14ac:dyDescent="0.25">
       <c r="A155">
         <v>154</v>
       </c>
@@ -6236,7 +6345,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="156" spans="1:7" x14ac:dyDescent="0.25">
+    <row r="156" spans="1:7" hidden="1" x14ac:dyDescent="0.25">
       <c r="A156">
         <v>155</v>
       </c>
@@ -6259,7 +6368,7 @@
         <v>2.189E-2</v>
       </c>
     </row>
-    <row r="157" spans="1:7" x14ac:dyDescent="0.25">
+    <row r="157" spans="1:7" hidden="1" x14ac:dyDescent="0.25">
       <c r="A157">
         <v>156</v>
       </c>
@@ -6282,7 +6391,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="158" spans="1:7" x14ac:dyDescent="0.25">
+    <row r="158" spans="1:7" hidden="1" x14ac:dyDescent="0.25">
       <c r="A158">
         <v>157</v>
       </c>
@@ -6305,7 +6414,7 @@
         <v>0.51226666666666665</v>
       </c>
     </row>
-    <row r="159" spans="1:7" x14ac:dyDescent="0.25">
+    <row r="159" spans="1:7" hidden="1" x14ac:dyDescent="0.25">
       <c r="A159">
         <v>158</v>
       </c>
@@ -6351,7 +6460,7 @@
         <v>2.5753333333333336E-2</v>
       </c>
     </row>
-    <row r="161" spans="1:7" x14ac:dyDescent="0.25">
+    <row r="161" spans="1:7" hidden="1" x14ac:dyDescent="0.25">
       <c r="A161">
         <v>160</v>
       </c>
@@ -6374,7 +6483,7 @@
         <v>1.6799999999999999E-2</v>
       </c>
     </row>
-    <row r="162" spans="1:7" x14ac:dyDescent="0.25">
+    <row r="162" spans="1:7" hidden="1" x14ac:dyDescent="0.25">
       <c r="A162">
         <v>161</v>
       </c>
@@ -6397,7 +6506,7 @@
         <v>8.1466666666666666E-3</v>
       </c>
     </row>
-    <row r="163" spans="1:7" x14ac:dyDescent="0.25">
+    <row r="163" spans="1:7" hidden="1" x14ac:dyDescent="0.25">
       <c r="A163">
         <v>162</v>
       </c>
@@ -6420,7 +6529,7 @@
         <v>6.2599999999999999E-3</v>
       </c>
     </row>
-    <row r="164" spans="1:7" x14ac:dyDescent="0.25">
+    <row r="164" spans="1:7" hidden="1" x14ac:dyDescent="0.25">
       <c r="A164">
         <v>163</v>
       </c>
@@ -6443,7 +6552,7 @@
         <v>5.7666666666666665E-3</v>
       </c>
     </row>
-    <row r="165" spans="1:7" x14ac:dyDescent="0.25">
+    <row r="165" spans="1:7" hidden="1" x14ac:dyDescent="0.25">
       <c r="A165">
         <v>164</v>
       </c>
@@ -6466,7 +6575,7 @@
         <v>0.11810666666666668</v>
       </c>
     </row>
-    <row r="166" spans="1:7" x14ac:dyDescent="0.25">
+    <row r="166" spans="1:7" hidden="1" x14ac:dyDescent="0.25">
       <c r="A166">
         <v>165</v>
       </c>
@@ -6489,7 +6598,7 @@
         <v>3.8666666666666671E-3</v>
       </c>
     </row>
-    <row r="167" spans="1:7" x14ac:dyDescent="0.25">
+    <row r="167" spans="1:7" hidden="1" x14ac:dyDescent="0.25">
       <c r="A167">
         <v>166</v>
       </c>
@@ -6512,7 +6621,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="168" spans="1:7" x14ac:dyDescent="0.25">
+    <row r="168" spans="1:7" hidden="1" x14ac:dyDescent="0.25">
       <c r="A168">
         <v>167</v>
       </c>
@@ -6535,7 +6644,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="169" spans="1:7" x14ac:dyDescent="0.25">
+    <row r="169" spans="1:7" hidden="1" x14ac:dyDescent="0.25">
       <c r="A169">
         <v>168</v>
       </c>
@@ -6558,7 +6667,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="170" spans="1:7" x14ac:dyDescent="0.25">
+    <row r="170" spans="1:7" hidden="1" x14ac:dyDescent="0.25">
       <c r="A170">
         <v>169</v>
       </c>
@@ -6581,7 +6690,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="171" spans="1:7" x14ac:dyDescent="0.25">
+    <row r="171" spans="1:7" hidden="1" x14ac:dyDescent="0.25">
       <c r="A171">
         <v>170</v>
       </c>
@@ -6604,7 +6713,7 @@
         <v>1.3633333333333334E-3</v>
       </c>
     </row>
-    <row r="172" spans="1:7" x14ac:dyDescent="0.25">
+    <row r="172" spans="1:7" hidden="1" x14ac:dyDescent="0.25">
       <c r="A172">
         <v>171</v>
       </c>
@@ -6627,7 +6736,7 @@
         <v>2.4433333333333335E-2</v>
       </c>
     </row>
-    <row r="173" spans="1:7" x14ac:dyDescent="0.25">
+    <row r="173" spans="1:7" hidden="1" x14ac:dyDescent="0.25">
       <c r="A173">
         <v>172</v>
       </c>
@@ -6650,7 +6759,7 @@
         <v>6.5176666666666674E-2</v>
       </c>
     </row>
-    <row r="174" spans="1:7" x14ac:dyDescent="0.25">
+    <row r="174" spans="1:7" hidden="1" x14ac:dyDescent="0.25">
       <c r="A174">
         <v>173</v>
       </c>
@@ -6673,7 +6782,7 @@
         <v>2.6346666666666664E-2</v>
       </c>
     </row>
-    <row r="175" spans="1:7" x14ac:dyDescent="0.25">
+    <row r="175" spans="1:7" hidden="1" x14ac:dyDescent="0.25">
       <c r="A175">
         <v>174</v>
       </c>
@@ -6696,7 +6805,7 @@
         <v>7.273333333333333E-2</v>
       </c>
     </row>
-    <row r="176" spans="1:7" x14ac:dyDescent="0.25">
+    <row r="176" spans="1:7" hidden="1" x14ac:dyDescent="0.25">
       <c r="A176">
         <v>175</v>
       </c>
@@ -6719,7 +6828,7 @@
         <v>2.0313333333333336E-2</v>
       </c>
     </row>
-    <row r="177" spans="1:7" x14ac:dyDescent="0.25">
+    <row r="177" spans="1:7" hidden="1" x14ac:dyDescent="0.25">
       <c r="A177">
         <v>176</v>
       </c>
@@ -6742,7 +6851,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="178" spans="1:7" x14ac:dyDescent="0.25">
+    <row r="178" spans="1:7" hidden="1" x14ac:dyDescent="0.25">
       <c r="A178">
         <v>177</v>
       </c>
@@ -6765,7 +6874,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="179" spans="1:7" x14ac:dyDescent="0.25">
+    <row r="179" spans="1:7" hidden="1" x14ac:dyDescent="0.25">
       <c r="A179">
         <v>178</v>
       </c>
@@ -6788,7 +6897,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="180" spans="1:7" x14ac:dyDescent="0.25">
+    <row r="180" spans="1:7" hidden="1" x14ac:dyDescent="0.25">
       <c r="A180">
         <v>179</v>
       </c>
@@ -6811,7 +6920,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="181" spans="1:7" x14ac:dyDescent="0.25">
+    <row r="181" spans="1:7" hidden="1" x14ac:dyDescent="0.25">
       <c r="A181">
         <v>180</v>
       </c>
@@ -6834,7 +6943,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="182" spans="1:7" x14ac:dyDescent="0.25">
+    <row r="182" spans="1:7" hidden="1" x14ac:dyDescent="0.25">
       <c r="A182">
         <v>181</v>
       </c>
@@ -6857,7 +6966,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="183" spans="1:7" x14ac:dyDescent="0.25">
+    <row r="183" spans="1:7" hidden="1" x14ac:dyDescent="0.25">
       <c r="A183">
         <v>182</v>
       </c>
@@ -6880,7 +6989,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="184" spans="1:7" x14ac:dyDescent="0.25">
+    <row r="184" spans="1:7" hidden="1" x14ac:dyDescent="0.25">
       <c r="A184">
         <v>183</v>
       </c>
@@ -6903,7 +7012,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="185" spans="1:7" x14ac:dyDescent="0.25">
+    <row r="185" spans="1:7" hidden="1" x14ac:dyDescent="0.25">
       <c r="A185">
         <v>184</v>
       </c>
@@ -6926,7 +7035,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="186" spans="1:7" x14ac:dyDescent="0.25">
+    <row r="186" spans="1:7" hidden="1" x14ac:dyDescent="0.25">
       <c r="A186">
         <v>185</v>
       </c>
@@ -6949,7 +7058,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="187" spans="1:7" x14ac:dyDescent="0.25">
+    <row r="187" spans="1:7" hidden="1" x14ac:dyDescent="0.25">
       <c r="A187">
         <v>186</v>
       </c>
@@ -6972,7 +7081,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="188" spans="1:7" x14ac:dyDescent="0.25">
+    <row r="188" spans="1:7" hidden="1" x14ac:dyDescent="0.25">
       <c r="A188">
         <v>187</v>
       </c>
@@ -6995,7 +7104,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="189" spans="1:7" x14ac:dyDescent="0.25">
+    <row r="189" spans="1:7" hidden="1" x14ac:dyDescent="0.25">
       <c r="A189">
         <v>188</v>
       </c>
@@ -7018,7 +7127,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="190" spans="1:7" x14ac:dyDescent="0.25">
+    <row r="190" spans="1:7" hidden="1" x14ac:dyDescent="0.25">
       <c r="A190">
         <v>189</v>
       </c>
@@ -7041,7 +7150,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="191" spans="1:7" x14ac:dyDescent="0.25">
+    <row r="191" spans="1:7" hidden="1" x14ac:dyDescent="0.25">
       <c r="A191">
         <v>190</v>
       </c>
@@ -7064,7 +7173,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="192" spans="1:7" x14ac:dyDescent="0.25">
+    <row r="192" spans="1:7" hidden="1" x14ac:dyDescent="0.25">
       <c r="A192">
         <v>191</v>
       </c>
@@ -7087,7 +7196,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="193" spans="1:7" x14ac:dyDescent="0.25">
+    <row r="193" spans="1:7" hidden="1" x14ac:dyDescent="0.25">
       <c r="A193">
         <v>192</v>
       </c>
@@ -7110,7 +7219,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="194" spans="1:7" x14ac:dyDescent="0.25">
+    <row r="194" spans="1:7" hidden="1" x14ac:dyDescent="0.25">
       <c r="A194">
         <v>193</v>
       </c>
@@ -7133,7 +7242,7 @@
         <v>3.7000000000000002E-3</v>
       </c>
     </row>
-    <row r="195" spans="1:7" x14ac:dyDescent="0.25">
+    <row r="195" spans="1:7" hidden="1" x14ac:dyDescent="0.25">
       <c r="A195">
         <v>194</v>
       </c>
@@ -7156,7 +7265,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="196" spans="1:7" x14ac:dyDescent="0.25">
+    <row r="196" spans="1:7" hidden="1" x14ac:dyDescent="0.25">
       <c r="A196">
         <v>195</v>
       </c>
@@ -7179,7 +7288,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="197" spans="1:7" x14ac:dyDescent="0.25">
+    <row r="197" spans="1:7" hidden="1" x14ac:dyDescent="0.25">
       <c r="A197">
         <v>196</v>
       </c>
@@ -7202,7 +7311,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="198" spans="1:7" x14ac:dyDescent="0.25">
+    <row r="198" spans="1:7" hidden="1" x14ac:dyDescent="0.25">
       <c r="A198">
         <v>197</v>
       </c>
@@ -7225,7 +7334,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="199" spans="1:7" x14ac:dyDescent="0.25">
+    <row r="199" spans="1:7" hidden="1" x14ac:dyDescent="0.25">
       <c r="A199">
         <v>198</v>
       </c>
@@ -7248,7 +7357,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="200" spans="1:7" x14ac:dyDescent="0.25">
+    <row r="200" spans="1:7" hidden="1" x14ac:dyDescent="0.25">
       <c r="A200">
         <v>199</v>
       </c>
@@ -7271,7 +7380,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="201" spans="1:7" x14ac:dyDescent="0.25">
+    <row r="201" spans="1:7" hidden="1" x14ac:dyDescent="0.25">
       <c r="A201">
         <v>200</v>
       </c>
@@ -7294,7 +7403,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="202" spans="1:7" x14ac:dyDescent="0.25">
+    <row r="202" spans="1:7" hidden="1" x14ac:dyDescent="0.25">
       <c r="A202">
         <v>201</v>
       </c>
@@ -7317,7 +7426,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="203" spans="1:7" x14ac:dyDescent="0.25">
+    <row r="203" spans="1:7" hidden="1" x14ac:dyDescent="0.25">
       <c r="A203">
         <v>202</v>
       </c>
@@ -7340,7 +7449,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="204" spans="1:7" x14ac:dyDescent="0.25">
+    <row r="204" spans="1:7" hidden="1" x14ac:dyDescent="0.25">
       <c r="A204">
         <v>203</v>
       </c>
@@ -7363,7 +7472,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="205" spans="1:7" x14ac:dyDescent="0.25">
+    <row r="205" spans="1:7" hidden="1" x14ac:dyDescent="0.25">
       <c r="A205">
         <v>204</v>
       </c>
@@ -7386,7 +7495,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="206" spans="1:7" x14ac:dyDescent="0.25">
+    <row r="206" spans="1:7" hidden="1" x14ac:dyDescent="0.25">
       <c r="A206">
         <v>205</v>
       </c>
@@ -7409,7 +7518,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="207" spans="1:7" x14ac:dyDescent="0.25">
+    <row r="207" spans="1:7" hidden="1" x14ac:dyDescent="0.25">
       <c r="A207">
         <v>206</v>
       </c>
@@ -7432,7 +7541,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="208" spans="1:7" x14ac:dyDescent="0.25">
+    <row r="208" spans="1:7" hidden="1" x14ac:dyDescent="0.25">
       <c r="A208">
         <v>207</v>
       </c>
@@ -7455,7 +7564,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="209" spans="1:7" x14ac:dyDescent="0.25">
+    <row r="209" spans="1:7" hidden="1" x14ac:dyDescent="0.25">
       <c r="A209">
         <v>208</v>
       </c>
@@ -7478,7 +7587,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="210" spans="1:7" x14ac:dyDescent="0.25">
+    <row r="210" spans="1:7" hidden="1" x14ac:dyDescent="0.25">
       <c r="A210">
         <v>209</v>
       </c>
@@ -7501,7 +7610,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="211" spans="1:7" x14ac:dyDescent="0.25">
+    <row r="211" spans="1:7" hidden="1" x14ac:dyDescent="0.25">
       <c r="A211">
         <v>210</v>
       </c>
@@ -7524,7 +7633,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="212" spans="1:7" x14ac:dyDescent="0.25">
+    <row r="212" spans="1:7" hidden="1" x14ac:dyDescent="0.25">
       <c r="A212">
         <v>211</v>
       </c>
@@ -7547,7 +7656,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="213" spans="1:7" x14ac:dyDescent="0.25">
+    <row r="213" spans="1:7" hidden="1" x14ac:dyDescent="0.25">
       <c r="A213">
         <v>212</v>
       </c>
@@ -7570,7 +7679,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="214" spans="1:7" x14ac:dyDescent="0.25">
+    <row r="214" spans="1:7" hidden="1" x14ac:dyDescent="0.25">
       <c r="A214">
         <v>213</v>
       </c>
@@ -7593,7 +7702,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="215" spans="1:7" x14ac:dyDescent="0.25">
+    <row r="215" spans="1:7" hidden="1" x14ac:dyDescent="0.25">
       <c r="A215">
         <v>214</v>
       </c>
@@ -7616,7 +7725,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="216" spans="1:7" x14ac:dyDescent="0.25">
+    <row r="216" spans="1:7" hidden="1" x14ac:dyDescent="0.25">
       <c r="A216">
         <v>215</v>
       </c>
@@ -7639,7 +7748,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="217" spans="1:7" x14ac:dyDescent="0.25">
+    <row r="217" spans="1:7" hidden="1" x14ac:dyDescent="0.25">
       <c r="A217">
         <v>216</v>
       </c>
@@ -7662,7 +7771,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="218" spans="1:7" x14ac:dyDescent="0.25">
+    <row r="218" spans="1:7" hidden="1" x14ac:dyDescent="0.25">
       <c r="A218">
         <v>217</v>
       </c>
@@ -7685,7 +7794,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="219" spans="1:7" x14ac:dyDescent="0.25">
+    <row r="219" spans="1:7" hidden="1" x14ac:dyDescent="0.25">
       <c r="A219">
         <v>218</v>
       </c>
@@ -7708,7 +7817,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="220" spans="1:7" x14ac:dyDescent="0.25">
+    <row r="220" spans="1:7" hidden="1" x14ac:dyDescent="0.25">
       <c r="A220">
         <v>219</v>
       </c>
@@ -7731,7 +7840,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="221" spans="1:7" x14ac:dyDescent="0.25">
+    <row r="221" spans="1:7" hidden="1" x14ac:dyDescent="0.25">
       <c r="A221">
         <v>220</v>
       </c>
@@ -7754,7 +7863,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="222" spans="1:7" x14ac:dyDescent="0.25">
+    <row r="222" spans="1:7" hidden="1" x14ac:dyDescent="0.25">
       <c r="A222">
         <v>221</v>
       </c>
@@ -7777,7 +7886,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="223" spans="1:7" x14ac:dyDescent="0.25">
+    <row r="223" spans="1:7" hidden="1" x14ac:dyDescent="0.25">
       <c r="A223">
         <v>222</v>
       </c>
@@ -7800,7 +7909,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="224" spans="1:7" x14ac:dyDescent="0.25">
+    <row r="224" spans="1:7" hidden="1" x14ac:dyDescent="0.25">
       <c r="A224">
         <v>223</v>
       </c>
@@ -7823,7 +7932,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="225" spans="1:7" x14ac:dyDescent="0.25">
+    <row r="225" spans="1:7" hidden="1" x14ac:dyDescent="0.25">
       <c r="A225">
         <v>224</v>
       </c>
@@ -7846,7 +7955,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="226" spans="1:7" x14ac:dyDescent="0.25">
+    <row r="226" spans="1:7" hidden="1" x14ac:dyDescent="0.25">
       <c r="A226">
         <v>225</v>
       </c>
@@ -7869,7 +7978,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="227" spans="1:7" x14ac:dyDescent="0.25">
+    <row r="227" spans="1:7" hidden="1" x14ac:dyDescent="0.25">
       <c r="A227">
         <v>226</v>
       </c>
@@ -7892,7 +8001,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="228" spans="1:7" x14ac:dyDescent="0.25">
+    <row r="228" spans="1:7" hidden="1" x14ac:dyDescent="0.25">
       <c r="A228">
         <v>227</v>
       </c>
@@ -7915,7 +8024,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="229" spans="1:7" x14ac:dyDescent="0.25">
+    <row r="229" spans="1:7" hidden="1" x14ac:dyDescent="0.25">
       <c r="A229">
         <v>228</v>
       </c>
@@ -7938,7 +8047,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="230" spans="1:7" x14ac:dyDescent="0.25">
+    <row r="230" spans="1:7" hidden="1" x14ac:dyDescent="0.25">
       <c r="A230">
         <v>229</v>
       </c>
@@ -7961,7 +8070,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="231" spans="1:7" x14ac:dyDescent="0.25">
+    <row r="231" spans="1:7" hidden="1" x14ac:dyDescent="0.25">
       <c r="A231">
         <v>230</v>
       </c>
@@ -7984,7 +8093,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="232" spans="1:7" x14ac:dyDescent="0.25">
+    <row r="232" spans="1:7" hidden="1" x14ac:dyDescent="0.25">
       <c r="A232">
         <v>231</v>
       </c>
@@ -8007,7 +8116,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="233" spans="1:7" x14ac:dyDescent="0.25">
+    <row r="233" spans="1:7" hidden="1" x14ac:dyDescent="0.25">
       <c r="A233">
         <v>232</v>
       </c>
@@ -8030,7 +8139,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="234" spans="1:7" x14ac:dyDescent="0.25">
+    <row r="234" spans="1:7" hidden="1" x14ac:dyDescent="0.25">
       <c r="A234">
         <v>233</v>
       </c>
@@ -8053,7 +8162,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="235" spans="1:7" x14ac:dyDescent="0.25">
+    <row r="235" spans="1:7" hidden="1" x14ac:dyDescent="0.25">
       <c r="A235">
         <v>234</v>
       </c>
@@ -8076,7 +8185,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="236" spans="1:7" x14ac:dyDescent="0.25">
+    <row r="236" spans="1:7" hidden="1" x14ac:dyDescent="0.25">
       <c r="A236">
         <v>235</v>
       </c>
@@ -8099,7 +8208,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="237" spans="1:7" x14ac:dyDescent="0.25">
+    <row r="237" spans="1:7" hidden="1" x14ac:dyDescent="0.25">
       <c r="A237">
         <v>236</v>
       </c>
@@ -8122,7 +8231,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="238" spans="1:7" x14ac:dyDescent="0.25">
+    <row r="238" spans="1:7" hidden="1" x14ac:dyDescent="0.25">
       <c r="A238">
         <v>237</v>
       </c>
@@ -8145,7 +8254,7 @@
         <v>4.4690000000000001E-2</v>
       </c>
     </row>
-    <row r="239" spans="1:7" x14ac:dyDescent="0.25">
+    <row r="239" spans="1:7" hidden="1" x14ac:dyDescent="0.25">
       <c r="A239">
         <v>238</v>
       </c>
@@ -8168,7 +8277,7 @@
         <v>3.6630000000000003E-2</v>
       </c>
     </row>
-    <row r="240" spans="1:7" x14ac:dyDescent="0.25">
+    <row r="240" spans="1:7" hidden="1" x14ac:dyDescent="0.25">
       <c r="A240">
         <v>239</v>
       </c>
@@ -8191,7 +8300,7 @@
         <v>7.9310000000000005E-2</v>
       </c>
     </row>
-    <row r="241" spans="1:7" x14ac:dyDescent="0.25">
+    <row r="241" spans="1:7" hidden="1" x14ac:dyDescent="0.25">
       <c r="A241">
         <v>240</v>
       </c>
@@ -8214,7 +8323,7 @@
         <v>2.0483333333333333E-2</v>
       </c>
     </row>
-    <row r="242" spans="1:7" x14ac:dyDescent="0.25">
+    <row r="242" spans="1:7" hidden="1" x14ac:dyDescent="0.25">
       <c r="A242">
         <v>241</v>
       </c>
@@ -8237,7 +8346,7 @@
         <v>3.6499999999999998E-2</v>
       </c>
     </row>
-    <row r="243" spans="1:7" x14ac:dyDescent="0.25">
+    <row r="243" spans="1:7" hidden="1" x14ac:dyDescent="0.25">
       <c r="A243">
         <v>242</v>
       </c>
@@ -8260,7 +8369,7 @@
         <v>2.186666666666667E-2</v>
       </c>
     </row>
-    <row r="244" spans="1:7" x14ac:dyDescent="0.25">
+    <row r="244" spans="1:7" hidden="1" x14ac:dyDescent="0.25">
       <c r="A244">
         <v>243</v>
       </c>
@@ -8283,7 +8392,7 @@
         <v>3.5499999999999997E-2</v>
       </c>
     </row>
-    <row r="245" spans="1:7" x14ac:dyDescent="0.25">
+    <row r="245" spans="1:7" hidden="1" x14ac:dyDescent="0.25">
       <c r="A245">
         <v>244</v>
       </c>
@@ -8306,7 +8415,7 @@
         <v>2.6290000000000001E-2</v>
       </c>
     </row>
-    <row r="246" spans="1:7" x14ac:dyDescent="0.25">
+    <row r="246" spans="1:7" hidden="1" x14ac:dyDescent="0.25">
       <c r="A246">
         <v>245</v>
       </c>
@@ -8329,7 +8438,7 @@
         <v>3.1833333333333338E-2</v>
       </c>
     </row>
-    <row r="247" spans="1:7" x14ac:dyDescent="0.25">
+    <row r="247" spans="1:7" hidden="1" x14ac:dyDescent="0.25">
       <c r="A247">
         <v>246</v>
       </c>
@@ -8352,7 +8461,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="248" spans="1:7" x14ac:dyDescent="0.25">
+    <row r="248" spans="1:7" hidden="1" x14ac:dyDescent="0.25">
       <c r="A248">
         <v>247</v>
       </c>
@@ -8375,7 +8484,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="249" spans="1:7" x14ac:dyDescent="0.25">
+    <row r="249" spans="1:7" hidden="1" x14ac:dyDescent="0.25">
       <c r="A249">
         <v>248</v>
       </c>
@@ -8398,7 +8507,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="250" spans="1:7" x14ac:dyDescent="0.25">
+    <row r="250" spans="1:7" hidden="1" x14ac:dyDescent="0.25">
       <c r="A250">
         <v>249</v>
       </c>
@@ -8421,7 +8530,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="251" spans="1:7" x14ac:dyDescent="0.25">
+    <row r="251" spans="1:7" hidden="1" x14ac:dyDescent="0.25">
       <c r="A251">
         <v>250</v>
       </c>
@@ -8444,7 +8553,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="252" spans="1:7" x14ac:dyDescent="0.25">
+    <row r="252" spans="1:7" hidden="1" x14ac:dyDescent="0.25">
       <c r="A252">
         <v>251</v>
       </c>
@@ -8467,7 +8576,7 @@
         <v>1.46E-2</v>
       </c>
     </row>
-    <row r="253" spans="1:7" x14ac:dyDescent="0.25">
+    <row r="253" spans="1:7" hidden="1" x14ac:dyDescent="0.25">
       <c r="A253">
         <v>252</v>
       </c>
@@ -8490,7 +8599,7 @@
         <v>2.2000000000000002E-2</v>
       </c>
     </row>
-    <row r="254" spans="1:7" x14ac:dyDescent="0.25">
+    <row r="254" spans="1:7" hidden="1" x14ac:dyDescent="0.25">
       <c r="A254">
         <v>253</v>
       </c>
@@ -8513,7 +8622,7 @@
         <v>2.1700000000000001E-2</v>
       </c>
     </row>
-    <row r="255" spans="1:7" x14ac:dyDescent="0.25">
+    <row r="255" spans="1:7" hidden="1" x14ac:dyDescent="0.25">
       <c r="A255">
         <v>254</v>
       </c>
@@ -8536,7 +8645,7 @@
         <v>2.4580000000000001E-2</v>
       </c>
     </row>
-    <row r="256" spans="1:7" x14ac:dyDescent="0.25">
+    <row r="256" spans="1:7" hidden="1" x14ac:dyDescent="0.25">
       <c r="A256">
         <v>255</v>
       </c>
@@ -8559,7 +8668,7 @@
         <v>2.8466666666666661E-2</v>
       </c>
     </row>
-    <row r="257" spans="1:7" x14ac:dyDescent="0.25">
+    <row r="257" spans="1:7" hidden="1" x14ac:dyDescent="0.25">
       <c r="A257">
         <v>256</v>
       </c>
@@ -8582,7 +8691,7 @@
         <v>4.9436666666666663E-2</v>
       </c>
     </row>
-    <row r="258" spans="1:7" x14ac:dyDescent="0.25">
+    <row r="258" spans="1:7" hidden="1" x14ac:dyDescent="0.25">
       <c r="A258">
         <v>257</v>
       </c>
@@ -8605,7 +8714,7 @@
         <v>1.0396666666666665E-2</v>
       </c>
     </row>
-    <row r="259" spans="1:7" x14ac:dyDescent="0.25">
+    <row r="259" spans="1:7" hidden="1" x14ac:dyDescent="0.25">
       <c r="A259">
         <v>258</v>
       </c>
@@ -8628,7 +8737,7 @@
         <v>1.2800000000000001E-2</v>
       </c>
     </row>
-    <row r="260" spans="1:7" x14ac:dyDescent="0.25">
+    <row r="260" spans="1:7" hidden="1" x14ac:dyDescent="0.25">
       <c r="A260">
         <v>259</v>
       </c>
@@ -8651,7 +8760,7 @@
         <v>3.9019999999999999E-2</v>
       </c>
     </row>
-    <row r="261" spans="1:7" x14ac:dyDescent="0.25">
+    <row r="261" spans="1:7" hidden="1" x14ac:dyDescent="0.25">
       <c r="A261">
         <v>260</v>
       </c>
@@ -8674,7 +8783,7 @@
         <v>3.5690000000000006E-2</v>
       </c>
     </row>
-    <row r="262" spans="1:7" x14ac:dyDescent="0.25">
+    <row r="262" spans="1:7" hidden="1" x14ac:dyDescent="0.25">
       <c r="A262">
         <v>262</v>
       </c>
@@ -8697,7 +8806,7 @@
         <v>1.3033333333333332E-3</v>
       </c>
     </row>
-    <row r="263" spans="1:7" x14ac:dyDescent="0.25">
+    <row r="263" spans="1:7" hidden="1" x14ac:dyDescent="0.25">
       <c r="A263">
         <v>263</v>
       </c>
@@ -8720,7 +8829,7 @@
         <v>5.3781666666666672E-2</v>
       </c>
     </row>
-    <row r="264" spans="1:7" x14ac:dyDescent="0.25">
+    <row r="264" spans="1:7" hidden="1" x14ac:dyDescent="0.25">
       <c r="A264">
         <v>264</v>
       </c>
@@ -8743,7 +8852,7 @@
         <v>0.37290000000000001</v>
       </c>
     </row>
-    <row r="265" spans="1:7" x14ac:dyDescent="0.25">
+    <row r="265" spans="1:7" hidden="1" x14ac:dyDescent="0.25">
       <c r="A265">
         <v>265</v>
       </c>
@@ -8766,7 +8875,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="266" spans="1:7" x14ac:dyDescent="0.25">
+    <row r="266" spans="1:7" hidden="1" x14ac:dyDescent="0.25">
       <c r="A266">
         <v>266</v>
       </c>
@@ -8789,7 +8898,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="267" spans="1:7" x14ac:dyDescent="0.25">
+    <row r="267" spans="1:7" hidden="1" x14ac:dyDescent="0.25">
       <c r="A267">
         <v>267</v>
       </c>
@@ -8812,7 +8921,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="268" spans="1:7" x14ac:dyDescent="0.25">
+    <row r="268" spans="1:7" hidden="1" x14ac:dyDescent="0.25">
       <c r="A268">
         <v>268</v>
       </c>
@@ -8835,7 +8944,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="269" spans="1:7" x14ac:dyDescent="0.25">
+    <row r="269" spans="1:7" hidden="1" x14ac:dyDescent="0.25">
       <c r="A269">
         <v>269</v>
       </c>
@@ -8858,7 +8967,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="270" spans="1:7" x14ac:dyDescent="0.25">
+    <row r="270" spans="1:7" hidden="1" x14ac:dyDescent="0.25">
       <c r="A270">
         <v>270</v>
       </c>
@@ -8881,7 +8990,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="271" spans="1:7" x14ac:dyDescent="0.25">
+    <row r="271" spans="1:7" hidden="1" x14ac:dyDescent="0.25">
       <c r="A271">
         <v>271</v>
       </c>
@@ -8904,7 +9013,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="272" spans="1:7" x14ac:dyDescent="0.25">
+    <row r="272" spans="1:7" hidden="1" x14ac:dyDescent="0.25">
       <c r="A272">
         <v>272</v>
       </c>
@@ -8927,7 +9036,7 @@
         <v>3.1200000000000002E-2</v>
       </c>
     </row>
-    <row r="273" spans="1:7" x14ac:dyDescent="0.25">
+    <row r="273" spans="1:7" hidden="1" x14ac:dyDescent="0.25">
       <c r="A273">
         <v>273</v>
       </c>
@@ -8950,7 +9059,7 @@
         <v>5.7363333333333336E-2</v>
       </c>
     </row>
-    <row r="274" spans="1:7" x14ac:dyDescent="0.25">
+    <row r="274" spans="1:7" hidden="1" x14ac:dyDescent="0.25">
       <c r="A274">
         <v>274</v>
       </c>
@@ -8973,7 +9082,7 @@
         <v>2.130333333333333E-2</v>
       </c>
     </row>
-    <row r="275" spans="1:7" x14ac:dyDescent="0.25">
+    <row r="275" spans="1:7" hidden="1" x14ac:dyDescent="0.25">
       <c r="A275">
         <v>275</v>
       </c>
@@ -8996,7 +9105,7 @@
         <v>2.35E-2</v>
       </c>
     </row>
-    <row r="276" spans="1:7" x14ac:dyDescent="0.25">
+    <row r="276" spans="1:7" hidden="1" x14ac:dyDescent="0.25">
       <c r="A276">
         <v>276</v>
       </c>
@@ -9019,7 +9128,7 @@
         <v>4.9703333333333335E-2</v>
       </c>
     </row>
-    <row r="277" spans="1:7" x14ac:dyDescent="0.25">
+    <row r="277" spans="1:7" hidden="1" x14ac:dyDescent="0.25">
       <c r="A277">
         <v>277</v>
       </c>
@@ -9042,7 +9151,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="278" spans="1:7" x14ac:dyDescent="0.25">
+    <row r="278" spans="1:7" hidden="1" x14ac:dyDescent="0.25">
       <c r="A278">
         <v>278</v>
       </c>
@@ -9065,7 +9174,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="279" spans="1:7" x14ac:dyDescent="0.25">
+    <row r="279" spans="1:7" hidden="1" x14ac:dyDescent="0.25">
       <c r="A279">
         <v>279</v>
       </c>
@@ -9088,7 +9197,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="280" spans="1:7" x14ac:dyDescent="0.25">
+    <row r="280" spans="1:7" hidden="1" x14ac:dyDescent="0.25">
       <c r="A280">
         <v>280</v>
       </c>
@@ -9111,7 +9220,7 @@
         <v>3.1159999999999997E-2</v>
       </c>
     </row>
-    <row r="281" spans="1:7" x14ac:dyDescent="0.25">
+    <row r="281" spans="1:7" hidden="1" x14ac:dyDescent="0.25">
       <c r="A281">
         <v>281</v>
       </c>
@@ -9134,7 +9243,7 @@
         <v>1.5910000000000001E-2</v>
       </c>
     </row>
-    <row r="282" spans="1:7" x14ac:dyDescent="0.25">
+    <row r="282" spans="1:7" hidden="1" x14ac:dyDescent="0.25">
       <c r="A282">
         <v>282</v>
       </c>
@@ -9157,7 +9266,7 @@
         <v>2.0533333333333334E-2</v>
       </c>
     </row>
-    <row r="283" spans="1:7" x14ac:dyDescent="0.25">
+    <row r="283" spans="1:7" hidden="1" x14ac:dyDescent="0.25">
       <c r="A283">
         <v>283</v>
       </c>
@@ -9180,7 +9289,7 @@
         <v>2.4326666666666667E-2</v>
       </c>
     </row>
-    <row r="284" spans="1:7" x14ac:dyDescent="0.25">
+    <row r="284" spans="1:7" hidden="1" x14ac:dyDescent="0.25">
       <c r="A284">
         <v>284</v>
       </c>
@@ -9203,7 +9312,7 @@
         <v>3.0166666666666671E-2</v>
       </c>
     </row>
-    <row r="285" spans="1:7" x14ac:dyDescent="0.25">
+    <row r="285" spans="1:7" hidden="1" x14ac:dyDescent="0.25">
       <c r="A285">
         <v>285</v>
       </c>
@@ -9226,7 +9335,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="286" spans="1:7" x14ac:dyDescent="0.25">
+    <row r="286" spans="1:7" hidden="1" x14ac:dyDescent="0.25">
       <c r="A286">
         <v>286</v>
       </c>
@@ -9249,7 +9358,7 @@
         <v>2.2799999999999997E-2</v>
       </c>
     </row>
-    <row r="287" spans="1:7" x14ac:dyDescent="0.25">
+    <row r="287" spans="1:7" hidden="1" x14ac:dyDescent="0.25">
       <c r="A287">
         <v>287</v>
       </c>
@@ -9272,7 +9381,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="288" spans="1:7" x14ac:dyDescent="0.25">
+    <row r="288" spans="1:7" hidden="1" x14ac:dyDescent="0.25">
       <c r="A288">
         <v>288</v>
       </c>
@@ -9295,7 +9404,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="289" spans="1:7" x14ac:dyDescent="0.25">
+    <row r="289" spans="1:7" hidden="1" x14ac:dyDescent="0.25">
       <c r="A289">
         <v>289</v>
       </c>
@@ -9318,7 +9427,7 @@
         <v>2.164333333333333E-2</v>
       </c>
     </row>
-    <row r="290" spans="1:7" x14ac:dyDescent="0.25">
+    <row r="290" spans="1:7" hidden="1" x14ac:dyDescent="0.25">
       <c r="A290">
         <v>290</v>
       </c>
@@ -9341,7 +9450,7 @@
         <v>2.2203333333333332E-2</v>
       </c>
     </row>
-    <row r="291" spans="1:7" x14ac:dyDescent="0.25">
+    <row r="291" spans="1:7" hidden="1" x14ac:dyDescent="0.25">
       <c r="A291">
         <v>291</v>
       </c>
@@ -9364,7 +9473,7 @@
         <v>9.7210000000000005E-2</v>
       </c>
     </row>
-    <row r="292" spans="1:7" x14ac:dyDescent="0.25">
+    <row r="292" spans="1:7" hidden="1" x14ac:dyDescent="0.25">
       <c r="A292">
         <v>292</v>
       </c>
@@ -9387,7 +9496,7 @@
         <v>5.0799999999999998E-2</v>
       </c>
     </row>
-    <row r="293" spans="1:7" x14ac:dyDescent="0.25">
+    <row r="293" spans="1:7" hidden="1" x14ac:dyDescent="0.25">
       <c r="A293">
         <v>293</v>
       </c>
@@ -9410,7 +9519,7 @@
         <v>2.1000000000000001E-2</v>
       </c>
     </row>
-    <row r="294" spans="1:7" x14ac:dyDescent="0.25">
+    <row r="294" spans="1:7" hidden="1" x14ac:dyDescent="0.25">
       <c r="A294">
         <v>294</v>
       </c>
@@ -9433,7 +9542,7 @@
         <v>2.5183333333333332E-2</v>
       </c>
     </row>
-    <row r="295" spans="1:7" x14ac:dyDescent="0.25">
+    <row r="295" spans="1:7" hidden="1" x14ac:dyDescent="0.25">
       <c r="A295">
         <v>295</v>
       </c>
@@ -9456,7 +9565,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="296" spans="1:7" x14ac:dyDescent="0.25">
+    <row r="296" spans="1:7" hidden="1" x14ac:dyDescent="0.25">
       <c r="A296">
         <v>296</v>
       </c>
@@ -9479,7 +9588,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="297" spans="1:7" x14ac:dyDescent="0.25">
+    <row r="297" spans="1:7" hidden="1" x14ac:dyDescent="0.25">
       <c r="A297">
         <v>297</v>
       </c>
@@ -9502,7 +9611,7 @@
         <v>6.3899999999999998E-2</v>
       </c>
     </row>
-    <row r="298" spans="1:7" x14ac:dyDescent="0.25">
+    <row r="298" spans="1:7" hidden="1" x14ac:dyDescent="0.25">
       <c r="A298">
         <v>298</v>
       </c>
@@ -9525,7 +9634,7 @@
         <v>6.54E-2</v>
       </c>
     </row>
-    <row r="299" spans="1:7" x14ac:dyDescent="0.25">
+    <row r="299" spans="1:7" hidden="1" x14ac:dyDescent="0.25">
       <c r="A299">
         <v>299</v>
       </c>
@@ -9548,7 +9657,7 @@
         <v>0.17859999999999998</v>
       </c>
     </row>
-    <row r="300" spans="1:7" x14ac:dyDescent="0.25">
+    <row r="300" spans="1:7" hidden="1" x14ac:dyDescent="0.25">
       <c r="A300">
         <v>300</v>
       </c>
@@ -9571,7 +9680,7 @@
         <v>4.24E-2</v>
       </c>
     </row>
-    <row r="301" spans="1:7" x14ac:dyDescent="0.25">
+    <row r="301" spans="1:7" hidden="1" x14ac:dyDescent="0.25">
       <c r="A301">
         <v>301</v>
       </c>
@@ -9594,7 +9703,7 @@
         <v>6.4666666666666657E-3</v>
       </c>
     </row>
-    <row r="302" spans="1:7" x14ac:dyDescent="0.25">
+    <row r="302" spans="1:7" hidden="1" x14ac:dyDescent="0.25">
       <c r="A302">
         <v>302</v>
       </c>
@@ -9617,7 +9726,7 @@
         <v>3.5733333333333339E-2</v>
       </c>
     </row>
-    <row r="303" spans="1:7" x14ac:dyDescent="0.25">
+    <row r="303" spans="1:7" hidden="1" x14ac:dyDescent="0.25">
       <c r="A303">
         <v>303</v>
       </c>
@@ -9640,7 +9749,7 @@
         <v>1.966E-2</v>
       </c>
     </row>
-    <row r="304" spans="1:7" x14ac:dyDescent="0.25">
+    <row r="304" spans="1:7" hidden="1" x14ac:dyDescent="0.25">
       <c r="A304">
         <v>304</v>
       </c>
@@ -9663,7 +9772,7 @@
         <v>8.5103333333333336E-2</v>
       </c>
     </row>
-    <row r="305" spans="1:7" x14ac:dyDescent="0.25">
+    <row r="305" spans="1:7" hidden="1" x14ac:dyDescent="0.25">
       <c r="A305">
         <v>305</v>
       </c>
@@ -9686,7 +9795,7 @@
         <v>0.18420000000000003</v>
       </c>
     </row>
-    <row r="306" spans="1:7" x14ac:dyDescent="0.25">
+    <row r="306" spans="1:7" hidden="1" x14ac:dyDescent="0.25">
       <c r="A306">
         <v>306</v>
       </c>
@@ -9709,7 +9818,7 @@
         <v>7.4720000000000009E-2</v>
       </c>
     </row>
-    <row r="307" spans="1:7" x14ac:dyDescent="0.25">
+    <row r="307" spans="1:7" hidden="1" x14ac:dyDescent="0.25">
       <c r="A307">
         <v>307</v>
       </c>
@@ -9732,7 +9841,7 @@
         <v>0.23593333333333333</v>
       </c>
     </row>
-    <row r="308" spans="1:7" x14ac:dyDescent="0.25">
+    <row r="308" spans="1:7" hidden="1" x14ac:dyDescent="0.25">
       <c r="A308">
         <v>308</v>
       </c>
@@ -9755,7 +9864,7 @@
         <v>0.13866000000000001</v>
       </c>
     </row>
-    <row r="309" spans="1:7" x14ac:dyDescent="0.25">
+    <row r="309" spans="1:7" hidden="1" x14ac:dyDescent="0.25">
       <c r="A309">
         <v>309</v>
       </c>
@@ -9778,7 +9887,7 @@
         <v>0.30320000000000003</v>
       </c>
     </row>
-    <row r="310" spans="1:7" x14ac:dyDescent="0.25">
+    <row r="310" spans="1:7" hidden="1" x14ac:dyDescent="0.25">
       <c r="A310">
         <v>310</v>
       </c>
@@ -9801,7 +9910,7 @@
         <v>8.4023333333333325E-2</v>
       </c>
     </row>
-    <row r="311" spans="1:7" x14ac:dyDescent="0.25">
+    <row r="311" spans="1:7" hidden="1" x14ac:dyDescent="0.25">
       <c r="A311">
         <v>311</v>
       </c>
@@ -9824,7 +9933,7 @@
         <v>0.21833333333333332</v>
       </c>
     </row>
-    <row r="312" spans="1:7" x14ac:dyDescent="0.25">
+    <row r="312" spans="1:7" hidden="1" x14ac:dyDescent="0.25">
       <c r="A312">
         <v>312</v>
       </c>
@@ -9847,7 +9956,7 @@
         <v>9.3179999999999999E-2</v>
       </c>
     </row>
-    <row r="313" spans="1:7" x14ac:dyDescent="0.25">
+    <row r="313" spans="1:7" hidden="1" x14ac:dyDescent="0.25">
       <c r="A313">
         <v>313</v>
       </c>
@@ -9870,7 +9979,7 @@
         <v>0.24006666666666671</v>
       </c>
     </row>
-    <row r="314" spans="1:7" x14ac:dyDescent="0.25">
+    <row r="314" spans="1:7" hidden="1" x14ac:dyDescent="0.25">
       <c r="A314">
         <v>314</v>
       </c>
@@ -9893,7 +10002,7 @@
         <v>4.7599999999999996E-2</v>
       </c>
     </row>
-    <row r="315" spans="1:7" x14ac:dyDescent="0.25">
+    <row r="315" spans="1:7" hidden="1" x14ac:dyDescent="0.25">
       <c r="A315">
         <v>315</v>
       </c>
@@ -9916,7 +10025,7 @@
         <v>0.20626666666666665</v>
       </c>
     </row>
-    <row r="316" spans="1:7" x14ac:dyDescent="0.25">
+    <row r="316" spans="1:7" hidden="1" x14ac:dyDescent="0.25">
       <c r="A316">
         <v>316</v>
       </c>
@@ -9939,7 +10048,7 @@
         <v>0.11514333333333335</v>
       </c>
     </row>
-    <row r="317" spans="1:7" x14ac:dyDescent="0.25">
+    <row r="317" spans="1:7" hidden="1" x14ac:dyDescent="0.25">
       <c r="A317">
         <v>317</v>
       </c>
@@ -9962,7 +10071,7 @@
         <v>0.33843333333333336</v>
       </c>
     </row>
-    <row r="318" spans="1:7" x14ac:dyDescent="0.25">
+    <row r="318" spans="1:7" hidden="1" x14ac:dyDescent="0.25">
       <c r="A318">
         <v>318</v>
       </c>
@@ -9985,7 +10094,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="319" spans="1:7" x14ac:dyDescent="0.25">
+    <row r="319" spans="1:7" hidden="1" x14ac:dyDescent="0.25">
       <c r="A319">
         <v>319</v>
       </c>
@@ -10008,7 +10117,7 @@
         <v>4.1656666666666668E-2</v>
       </c>
     </row>
-    <row r="320" spans="1:7" x14ac:dyDescent="0.25">
+    <row r="320" spans="1:7" hidden="1" x14ac:dyDescent="0.25">
       <c r="A320">
         <v>320</v>
       </c>
@@ -10031,7 +10140,7 @@
         <v>1.7933333333333332E-2</v>
       </c>
     </row>
-    <row r="321" spans="1:7" x14ac:dyDescent="0.25">
+    <row r="321" spans="1:7" hidden="1" x14ac:dyDescent="0.25">
       <c r="A321">
         <v>321</v>
       </c>
@@ -10054,7 +10163,7 @@
         <v>1.9766666666666665E-2</v>
       </c>
     </row>
-    <row r="322" spans="1:7" x14ac:dyDescent="0.25">
+    <row r="322" spans="1:7" hidden="1" x14ac:dyDescent="0.25">
       <c r="A322">
         <v>322</v>
       </c>
@@ -10077,7 +10186,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="323" spans="1:7" x14ac:dyDescent="0.25">
+    <row r="323" spans="1:7" hidden="1" x14ac:dyDescent="0.25">
       <c r="A323">
         <v>323</v>
       </c>
@@ -10100,7 +10209,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="324" spans="1:7" x14ac:dyDescent="0.25">
+    <row r="324" spans="1:7" hidden="1" x14ac:dyDescent="0.25">
       <c r="A324">
         <v>324</v>
       </c>
@@ -10123,7 +10232,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="325" spans="1:7" x14ac:dyDescent="0.25">
+    <row r="325" spans="1:7" hidden="1" x14ac:dyDescent="0.25">
       <c r="A325">
         <v>325</v>
       </c>
@@ -10146,7 +10255,7 @@
         <v>2.2333333333333337E-3</v>
       </c>
     </row>
-    <row r="326" spans="1:7" x14ac:dyDescent="0.25">
+    <row r="326" spans="1:7" hidden="1" x14ac:dyDescent="0.25">
       <c r="A326">
         <v>326</v>
       </c>
@@ -10169,7 +10278,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="327" spans="1:7" x14ac:dyDescent="0.25">
+    <row r="327" spans="1:7" hidden="1" x14ac:dyDescent="0.25">
       <c r="A327">
         <v>327</v>
       </c>
@@ -10192,7 +10301,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="328" spans="1:7" x14ac:dyDescent="0.25">
+    <row r="328" spans="1:7" hidden="1" x14ac:dyDescent="0.25">
       <c r="A328">
         <v>328</v>
       </c>
@@ -10215,7 +10324,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="329" spans="1:7" x14ac:dyDescent="0.25">
+    <row r="329" spans="1:7" hidden="1" x14ac:dyDescent="0.25">
       <c r="A329">
         <v>329</v>
       </c>
@@ -10238,7 +10347,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="330" spans="1:7" x14ac:dyDescent="0.25">
+    <row r="330" spans="1:7" hidden="1" x14ac:dyDescent="0.25">
       <c r="A330">
         <v>330</v>
       </c>
@@ -10261,7 +10370,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="331" spans="1:7" x14ac:dyDescent="0.25">
+    <row r="331" spans="1:7" hidden="1" x14ac:dyDescent="0.25">
       <c r="A331">
         <v>331</v>
       </c>
@@ -10284,7 +10393,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="332" spans="1:7" x14ac:dyDescent="0.25">
+    <row r="332" spans="1:7" hidden="1" x14ac:dyDescent="0.25">
       <c r="A332">
         <v>332</v>
       </c>
@@ -10307,7 +10416,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="333" spans="1:7" x14ac:dyDescent="0.25">
+    <row r="333" spans="1:7" hidden="1" x14ac:dyDescent="0.25">
       <c r="A333">
         <v>333</v>
       </c>
@@ -10330,7 +10439,7 @@
         <v>1.1303333333333334E-2</v>
       </c>
     </row>
-    <row r="334" spans="1:7" x14ac:dyDescent="0.25">
+    <row r="334" spans="1:7" hidden="1" x14ac:dyDescent="0.25">
       <c r="A334">
         <v>334</v>
       </c>
@@ -10353,7 +10462,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="335" spans="1:7" x14ac:dyDescent="0.25">
+    <row r="335" spans="1:7" hidden="1" x14ac:dyDescent="0.25">
       <c r="A335">
         <v>335</v>
       </c>
@@ -10376,7 +10485,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="336" spans="1:7" x14ac:dyDescent="0.25">
+    <row r="336" spans="1:7" hidden="1" x14ac:dyDescent="0.25">
       <c r="A336">
         <v>336</v>
       </c>
@@ -10399,7 +10508,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="337" spans="1:7" x14ac:dyDescent="0.25">
+    <row r="337" spans="1:7" hidden="1" x14ac:dyDescent="0.25">
       <c r="A337">
         <v>337</v>
       </c>
@@ -10422,7 +10531,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="338" spans="1:7" x14ac:dyDescent="0.25">
+    <row r="338" spans="1:7" hidden="1" x14ac:dyDescent="0.25">
       <c r="A338">
         <v>338</v>
       </c>
@@ -10445,7 +10554,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="339" spans="1:7" x14ac:dyDescent="0.25">
+    <row r="339" spans="1:7" hidden="1" x14ac:dyDescent="0.25">
       <c r="A339">
         <v>339</v>
       </c>
@@ -10468,7 +10577,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="340" spans="1:7" x14ac:dyDescent="0.25">
+    <row r="340" spans="1:7" hidden="1" x14ac:dyDescent="0.25">
       <c r="A340">
         <v>340</v>
       </c>
@@ -10491,7 +10600,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="341" spans="1:7" x14ac:dyDescent="0.25">
+    <row r="341" spans="1:7" hidden="1" x14ac:dyDescent="0.25">
       <c r="A341">
         <v>341</v>
       </c>
@@ -10514,7 +10623,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="342" spans="1:7" x14ac:dyDescent="0.25">
+    <row r="342" spans="1:7" hidden="1" x14ac:dyDescent="0.25">
       <c r="A342">
         <v>342</v>
       </c>
@@ -10537,7 +10646,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="343" spans="1:7" x14ac:dyDescent="0.25">
+    <row r="343" spans="1:7" hidden="1" x14ac:dyDescent="0.25">
       <c r="A343">
         <v>343</v>
       </c>
@@ -10560,7 +10669,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="344" spans="1:7" x14ac:dyDescent="0.25">
+    <row r="344" spans="1:7" hidden="1" x14ac:dyDescent="0.25">
       <c r="A344">
         <v>344</v>
       </c>
@@ -10583,7 +10692,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="345" spans="1:7" x14ac:dyDescent="0.25">
+    <row r="345" spans="1:7" hidden="1" x14ac:dyDescent="0.25">
       <c r="A345">
         <v>345</v>
       </c>
@@ -10606,7 +10715,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="346" spans="1:7" x14ac:dyDescent="0.25">
+    <row r="346" spans="1:7" hidden="1" x14ac:dyDescent="0.25">
       <c r="A346">
         <v>346</v>
       </c>
@@ -10629,7 +10738,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="347" spans="1:7" x14ac:dyDescent="0.25">
+    <row r="347" spans="1:7" hidden="1" x14ac:dyDescent="0.25">
       <c r="A347">
         <v>347</v>
       </c>
@@ -10652,7 +10761,7 @@
         <v>5.5453333333333327E-2</v>
       </c>
     </row>
-    <row r="348" spans="1:7" x14ac:dyDescent="0.25">
+    <row r="348" spans="1:7" hidden="1" x14ac:dyDescent="0.25">
       <c r="A348">
         <v>348</v>
       </c>
@@ -10675,7 +10784,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="349" spans="1:7" x14ac:dyDescent="0.25">
+    <row r="349" spans="1:7" hidden="1" x14ac:dyDescent="0.25">
       <c r="A349">
         <v>349</v>
       </c>
@@ -10698,7 +10807,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="350" spans="1:7" x14ac:dyDescent="0.25">
+    <row r="350" spans="1:7" hidden="1" x14ac:dyDescent="0.25">
       <c r="A350">
         <v>350</v>
       </c>
@@ -10721,7 +10830,7 @@
         <v>0.11868333333333334</v>
       </c>
     </row>
-    <row r="351" spans="1:7" x14ac:dyDescent="0.25">
+    <row r="351" spans="1:7" hidden="1" x14ac:dyDescent="0.25">
       <c r="A351">
         <v>351</v>
       </c>
@@ -10836,7 +10945,7 @@
         <v>6.2233333333333335E-2</v>
       </c>
     </row>
-    <row r="356" spans="1:7" x14ac:dyDescent="0.25">
+    <row r="356" spans="1:7" hidden="1" x14ac:dyDescent="0.25">
       <c r="A356">
         <v>356</v>
       </c>
@@ -10859,7 +10968,7 @@
         <v>0.12356666666666667</v>
       </c>
     </row>
-    <row r="357" spans="1:7" x14ac:dyDescent="0.25">
+    <row r="357" spans="1:7" hidden="1" x14ac:dyDescent="0.25">
       <c r="A357">
         <v>357</v>
       </c>
@@ -10882,7 +10991,7 @@
         <v>1.9089999999999999E-2</v>
       </c>
     </row>
-    <row r="358" spans="1:7" x14ac:dyDescent="0.25">
+    <row r="358" spans="1:7" hidden="1" x14ac:dyDescent="0.25">
       <c r="A358">
         <v>358</v>
       </c>
@@ -10905,7 +11014,7 @@
         <v>1.1876666666666667E-2</v>
       </c>
     </row>
-    <row r="359" spans="1:7" x14ac:dyDescent="0.25">
+    <row r="359" spans="1:7" hidden="1" x14ac:dyDescent="0.25">
       <c r="A359">
         <v>359</v>
       </c>
@@ -10928,7 +11037,7 @@
         <v>0.21313666666666667</v>
       </c>
     </row>
-    <row r="360" spans="1:7" x14ac:dyDescent="0.25">
+    <row r="360" spans="1:7" hidden="1" x14ac:dyDescent="0.25">
       <c r="A360">
         <v>360</v>
       </c>
@@ -10951,7 +11060,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="361" spans="1:7" x14ac:dyDescent="0.25">
+    <row r="361" spans="1:7" hidden="1" x14ac:dyDescent="0.25">
       <c r="A361">
         <v>361</v>
       </c>
@@ -10974,7 +11083,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="362" spans="1:7" x14ac:dyDescent="0.25">
+    <row r="362" spans="1:7" hidden="1" x14ac:dyDescent="0.25">
       <c r="A362">
         <v>362</v>
       </c>
@@ -10997,7 +11106,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="363" spans="1:7" x14ac:dyDescent="0.25">
+    <row r="363" spans="1:7" hidden="1" x14ac:dyDescent="0.25">
       <c r="A363">
         <v>363</v>
       </c>
@@ -11020,7 +11129,7 @@
         <v>1.6533333333333334E-2</v>
       </c>
     </row>
-    <row r="364" spans="1:7" x14ac:dyDescent="0.25">
+    <row r="364" spans="1:7" hidden="1" x14ac:dyDescent="0.25">
       <c r="A364">
         <v>364</v>
       </c>
@@ -11043,7 +11152,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="365" spans="1:7" x14ac:dyDescent="0.25">
+    <row r="365" spans="1:7" hidden="1" x14ac:dyDescent="0.25">
       <c r="A365">
         <v>365</v>
       </c>
@@ -11066,7 +11175,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="366" spans="1:7" x14ac:dyDescent="0.25">
+    <row r="366" spans="1:7" hidden="1" x14ac:dyDescent="0.25">
       <c r="A366">
         <v>367</v>
       </c>
@@ -11089,7 +11198,7 @@
         <v>2.1666666666666666E-3</v>
       </c>
     </row>
-    <row r="367" spans="1:7" x14ac:dyDescent="0.25">
+    <row r="367" spans="1:7" hidden="1" x14ac:dyDescent="0.25">
       <c r="A367">
         <v>368</v>
       </c>
@@ -11112,7 +11221,7 @@
         <v>7.1666666666666667E-3</v>
       </c>
     </row>
-    <row r="368" spans="1:7" x14ac:dyDescent="0.25">
+    <row r="368" spans="1:7" hidden="1" x14ac:dyDescent="0.25">
       <c r="A368">
         <v>369</v>
       </c>
@@ -11135,7 +11244,7 @@
         <v>2.299E-2</v>
       </c>
     </row>
-    <row r="369" spans="1:7" x14ac:dyDescent="0.25">
+    <row r="369" spans="1:7" hidden="1" x14ac:dyDescent="0.25">
       <c r="A369">
         <v>370</v>
       </c>
@@ -11158,7 +11267,7 @@
         <v>2.3859999999999996E-2</v>
       </c>
     </row>
-    <row r="370" spans="1:7" x14ac:dyDescent="0.25">
+    <row r="370" spans="1:7" hidden="1" x14ac:dyDescent="0.25">
       <c r="A370">
         <v>371</v>
       </c>
@@ -11181,7 +11290,7 @@
         <v>5.0743333333333328E-2</v>
       </c>
     </row>
-    <row r="371" spans="1:7" x14ac:dyDescent="0.25">
+    <row r="371" spans="1:7" hidden="1" x14ac:dyDescent="0.25">
       <c r="A371">
         <v>372</v>
       </c>
@@ -11204,7 +11313,7 @@
         <v>1.7766666666666667E-2</v>
       </c>
     </row>
-    <row r="372" spans="1:7" x14ac:dyDescent="0.25">
+    <row r="372" spans="1:7" hidden="1" x14ac:dyDescent="0.25">
       <c r="A372">
         <v>373</v>
       </c>
@@ -11227,7 +11336,7 @@
         <v>4.8266666666666673E-2</v>
       </c>
     </row>
-    <row r="373" spans="1:7" x14ac:dyDescent="0.25">
+    <row r="373" spans="1:7" hidden="1" x14ac:dyDescent="0.25">
       <c r="A373">
         <v>374</v>
       </c>
@@ -11273,7 +11382,7 @@
         <v>2.6533333333333329E-2</v>
       </c>
     </row>
-    <row r="375" spans="1:7" x14ac:dyDescent="0.25">
+    <row r="375" spans="1:7" hidden="1" x14ac:dyDescent="0.25">
       <c r="A375">
         <v>376</v>
       </c>
@@ -11296,7 +11405,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="376" spans="1:7" x14ac:dyDescent="0.25">
+    <row r="376" spans="1:7" hidden="1" x14ac:dyDescent="0.25">
       <c r="A376">
         <v>377</v>
       </c>
@@ -11319,7 +11428,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="377" spans="1:7" x14ac:dyDescent="0.25">
+    <row r="377" spans="1:7" hidden="1" x14ac:dyDescent="0.25">
       <c r="A377">
         <v>378</v>
       </c>
@@ -11572,7 +11681,7 @@
         <v>4.2199999999999998E-3</v>
       </c>
     </row>
-    <row r="388" spans="1:7" x14ac:dyDescent="0.25">
+    <row r="388" spans="1:7" hidden="1" x14ac:dyDescent="0.25">
       <c r="A388">
         <v>389</v>
       </c>
@@ -11595,7 +11704,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="389" spans="1:7" x14ac:dyDescent="0.25">
+    <row r="389" spans="1:7" hidden="1" x14ac:dyDescent="0.25">
       <c r="A389">
         <v>390</v>
       </c>
@@ -11618,7 +11727,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="390" spans="1:7" x14ac:dyDescent="0.25">
+    <row r="390" spans="1:7" hidden="1" x14ac:dyDescent="0.25">
       <c r="A390">
         <v>391</v>
       </c>
@@ -11641,7 +11750,7 @@
         <v>6.836666666666668E-3</v>
       </c>
     </row>
-    <row r="391" spans="1:7" x14ac:dyDescent="0.25">
+    <row r="391" spans="1:7" hidden="1" x14ac:dyDescent="0.25">
       <c r="A391">
         <v>392</v>
       </c>
@@ -11664,7 +11773,7 @@
         <v>6.4566666666666661E-3</v>
       </c>
     </row>
-    <row r="392" spans="1:7" x14ac:dyDescent="0.25">
+    <row r="392" spans="1:7" hidden="1" x14ac:dyDescent="0.25">
       <c r="A392">
         <v>393</v>
       </c>
@@ -11687,7 +11796,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="393" spans="1:7" x14ac:dyDescent="0.25">
+    <row r="393" spans="1:7" hidden="1" x14ac:dyDescent="0.25">
       <c r="A393">
         <v>396</v>
       </c>
@@ -11710,7 +11819,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="394" spans="1:7" x14ac:dyDescent="0.25">
+    <row r="394" spans="1:7" hidden="1" x14ac:dyDescent="0.25">
       <c r="A394">
         <v>397</v>
       </c>
@@ -11733,7 +11842,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="395" spans="1:7" x14ac:dyDescent="0.25">
+    <row r="395" spans="1:7" hidden="1" x14ac:dyDescent="0.25">
       <c r="A395">
         <v>398</v>
       </c>
@@ -11756,7 +11865,7 @@
         <v>7.8623333333333323E-2</v>
       </c>
     </row>
-    <row r="396" spans="1:7" x14ac:dyDescent="0.25">
+    <row r="396" spans="1:7" hidden="1" x14ac:dyDescent="0.25">
       <c r="A396">
         <v>399</v>
       </c>
@@ -11779,7 +11888,7 @@
         <v>0.16936666666666667</v>
       </c>
     </row>
-    <row r="397" spans="1:7" x14ac:dyDescent="0.25">
+    <row r="397" spans="1:7" hidden="1" x14ac:dyDescent="0.25">
       <c r="A397">
         <v>400</v>
       </c>
@@ -11802,7 +11911,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="398" spans="1:7" x14ac:dyDescent="0.25">
+    <row r="398" spans="1:7" hidden="1" x14ac:dyDescent="0.25">
       <c r="A398">
         <v>401</v>
       </c>
@@ -11825,7 +11934,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="399" spans="1:7" x14ac:dyDescent="0.25">
+    <row r="399" spans="1:7" hidden="1" x14ac:dyDescent="0.25">
       <c r="A399">
         <v>402</v>
       </c>
@@ -11848,7 +11957,7 @@
         <v>1.1816666666666666E-2</v>
       </c>
     </row>
-    <row r="400" spans="1:7" x14ac:dyDescent="0.25">
+    <row r="400" spans="1:7" hidden="1" x14ac:dyDescent="0.25">
       <c r="A400">
         <v>403</v>
       </c>
@@ -11871,7 +11980,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="401" spans="1:7" x14ac:dyDescent="0.25">
+    <row r="401" spans="1:7" hidden="1" x14ac:dyDescent="0.25">
       <c r="A401">
         <v>404</v>
       </c>
@@ -11894,7 +12003,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="402" spans="1:7" x14ac:dyDescent="0.25">
+    <row r="402" spans="1:7" hidden="1" x14ac:dyDescent="0.25">
       <c r="A402">
         <v>405</v>
       </c>
@@ -11917,7 +12026,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="403" spans="1:7" x14ac:dyDescent="0.25">
+    <row r="403" spans="1:7" hidden="1" x14ac:dyDescent="0.25">
       <c r="A403">
         <v>406</v>
       </c>
@@ -11940,7 +12049,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="404" spans="1:7" x14ac:dyDescent="0.25">
+    <row r="404" spans="1:7" hidden="1" x14ac:dyDescent="0.25">
       <c r="A404">
         <v>407</v>
       </c>
@@ -11963,7 +12072,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="405" spans="1:7" x14ac:dyDescent="0.25">
+    <row r="405" spans="1:7" hidden="1" x14ac:dyDescent="0.25">
       <c r="A405">
         <v>408</v>
       </c>
@@ -11986,7 +12095,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="406" spans="1:7" x14ac:dyDescent="0.25">
+    <row r="406" spans="1:7" hidden="1" x14ac:dyDescent="0.25">
       <c r="A406">
         <v>409</v>
       </c>
@@ -12055,7 +12164,7 @@
         <v>1.3466666666666667E-2</v>
       </c>
     </row>
-    <row r="409" spans="1:7" x14ac:dyDescent="0.25">
+    <row r="409" spans="1:7" hidden="1" x14ac:dyDescent="0.25">
       <c r="A409">
         <v>412</v>
       </c>
@@ -12078,7 +12187,7 @@
         <v>7.7666666666666674E-3</v>
       </c>
     </row>
-    <row r="410" spans="1:7" x14ac:dyDescent="0.25">
+    <row r="410" spans="1:7" hidden="1" x14ac:dyDescent="0.25">
       <c r="A410">
         <v>413</v>
       </c>
@@ -12101,7 +12210,7 @@
         <v>0.134435</v>
       </c>
     </row>
-    <row r="411" spans="1:7" x14ac:dyDescent="0.25">
+    <row r="411" spans="1:7" hidden="1" x14ac:dyDescent="0.25">
       <c r="A411">
         <v>414</v>
       </c>
@@ -12170,7 +12279,7 @@
         <v>1.0426666666666666E-2</v>
       </c>
     </row>
-    <row r="414" spans="1:7" x14ac:dyDescent="0.25">
+    <row r="414" spans="1:7" hidden="1" x14ac:dyDescent="0.25">
       <c r="A414">
         <v>417</v>
       </c>
@@ -12193,7 +12302,7 @@
         <v>1.5566666666666666E-2</v>
       </c>
     </row>
-    <row r="415" spans="1:7" x14ac:dyDescent="0.25">
+    <row r="415" spans="1:7" hidden="1" x14ac:dyDescent="0.25">
       <c r="A415">
         <v>418</v>
       </c>
@@ -12216,7 +12325,7 @@
         <v>1.8766666666666668E-2</v>
       </c>
     </row>
-    <row r="416" spans="1:7" x14ac:dyDescent="0.25">
+    <row r="416" spans="1:7" hidden="1" x14ac:dyDescent="0.25">
       <c r="A416">
         <v>419</v>
       </c>
@@ -12239,7 +12348,7 @@
         <v>7.8166666666666676E-2</v>
       </c>
     </row>
-    <row r="417" spans="1:7" x14ac:dyDescent="0.25">
+    <row r="417" spans="1:7" hidden="1" x14ac:dyDescent="0.25">
       <c r="A417">
         <v>420</v>
       </c>
@@ -12308,7 +12417,7 @@
         <v>1.6333333333333335E-2</v>
       </c>
     </row>
-    <row r="420" spans="1:7" x14ac:dyDescent="0.25">
+    <row r="420" spans="1:7" hidden="1" x14ac:dyDescent="0.25">
       <c r="A420">
         <v>423</v>
       </c>
@@ -12354,7 +12463,7 @@
         <v>2.0666666666666663E-2</v>
       </c>
     </row>
-    <row r="422" spans="1:7" x14ac:dyDescent="0.25">
+    <row r="422" spans="1:7" hidden="1" x14ac:dyDescent="0.25">
       <c r="A422">
         <v>425</v>
       </c>
@@ -12377,7 +12486,7 @@
         <v>2.1600000000000001E-2</v>
       </c>
     </row>
-    <row r="423" spans="1:7" x14ac:dyDescent="0.25">
+    <row r="423" spans="1:7" hidden="1" x14ac:dyDescent="0.25">
       <c r="A423">
         <v>426</v>
       </c>
@@ -12400,7 +12509,7 @@
         <v>3.3066666666666668E-2</v>
       </c>
     </row>
-    <row r="424" spans="1:7" x14ac:dyDescent="0.25">
+    <row r="424" spans="1:7" hidden="1" x14ac:dyDescent="0.25">
       <c r="A424">
         <v>427</v>
       </c>
@@ -12423,7 +12532,7 @@
         <v>3.633333333333333E-3</v>
       </c>
     </row>
-    <row r="425" spans="1:7" x14ac:dyDescent="0.25">
+    <row r="425" spans="1:7" hidden="1" x14ac:dyDescent="0.25">
       <c r="A425">
         <v>428</v>
       </c>
@@ -12446,7 +12555,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="426" spans="1:7" x14ac:dyDescent="0.25">
+    <row r="426" spans="1:7" hidden="1" x14ac:dyDescent="0.25">
       <c r="A426">
         <v>429</v>
       </c>
@@ -12469,7 +12578,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="427" spans="1:7" x14ac:dyDescent="0.25">
+    <row r="427" spans="1:7" hidden="1" x14ac:dyDescent="0.25">
       <c r="A427">
         <v>430</v>
       </c>
@@ -12515,7 +12624,7 @@
         <v>1.1366666666666667E-2</v>
       </c>
     </row>
-    <row r="429" spans="1:7" x14ac:dyDescent="0.25">
+    <row r="429" spans="1:7" hidden="1" x14ac:dyDescent="0.25">
       <c r="A429">
         <v>432</v>
       </c>
@@ -12538,7 +12647,7 @@
         <v>5.0599999999999985E-3</v>
       </c>
     </row>
-    <row r="430" spans="1:7" x14ac:dyDescent="0.25">
+    <row r="430" spans="1:7" hidden="1" x14ac:dyDescent="0.25">
       <c r="A430">
         <v>433</v>
       </c>
@@ -12561,7 +12670,7 @@
         <v>3.5366666666666663E-3</v>
       </c>
     </row>
-    <row r="431" spans="1:7" x14ac:dyDescent="0.25">
+    <row r="431" spans="1:7" hidden="1" x14ac:dyDescent="0.25">
       <c r="A431">
         <v>434</v>
       </c>
@@ -12584,7 +12693,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="432" spans="1:7" x14ac:dyDescent="0.25">
+    <row r="432" spans="1:7" hidden="1" x14ac:dyDescent="0.25">
       <c r="A432">
         <v>435</v>
       </c>
@@ -12607,7 +12716,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="433" spans="1:7" x14ac:dyDescent="0.25">
+    <row r="433" spans="1:7" hidden="1" x14ac:dyDescent="0.25">
       <c r="A433">
         <v>436</v>
       </c>
@@ -12630,7 +12739,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="434" spans="1:7" x14ac:dyDescent="0.25">
+    <row r="434" spans="1:7" hidden="1" x14ac:dyDescent="0.25">
       <c r="A434">
         <v>437</v>
       </c>
@@ -12653,7 +12762,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="435" spans="1:7" x14ac:dyDescent="0.25">
+    <row r="435" spans="1:7" hidden="1" x14ac:dyDescent="0.25">
       <c r="A435">
         <v>438</v>
       </c>
@@ -12676,7 +12785,7 @@
         <v>6.6666666666666662E-3</v>
       </c>
     </row>
-    <row r="436" spans="1:7" x14ac:dyDescent="0.25">
+    <row r="436" spans="1:7" hidden="1" x14ac:dyDescent="0.25">
       <c r="A436">
         <v>439</v>
       </c>
@@ -12699,7 +12808,7 @@
         <v>6.3666666666666672E-3</v>
       </c>
     </row>
-    <row r="437" spans="1:7" x14ac:dyDescent="0.25">
+    <row r="437" spans="1:7" hidden="1" x14ac:dyDescent="0.25">
       <c r="A437">
         <v>440</v>
       </c>
@@ -12722,7 +12831,7 @@
         <v>4.07E-2</v>
       </c>
     </row>
-    <row r="438" spans="1:7" x14ac:dyDescent="0.25">
+    <row r="438" spans="1:7" hidden="1" x14ac:dyDescent="0.25">
       <c r="A438">
         <v>441</v>
       </c>
@@ -12745,7 +12854,7 @@
         <v>2.1930000000000002E-2</v>
       </c>
     </row>
-    <row r="439" spans="1:7" x14ac:dyDescent="0.25">
+    <row r="439" spans="1:7" hidden="1" x14ac:dyDescent="0.25">
       <c r="A439">
         <v>442</v>
       </c>
@@ -12768,7 +12877,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="440" spans="1:7" x14ac:dyDescent="0.25">
+    <row r="440" spans="1:7" hidden="1" x14ac:dyDescent="0.25">
       <c r="A440">
         <v>443</v>
       </c>
@@ -12791,7 +12900,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="441" spans="1:7" x14ac:dyDescent="0.25">
+    <row r="441" spans="1:7" hidden="1" x14ac:dyDescent="0.25">
       <c r="A441">
         <v>444</v>
       </c>
@@ -12814,7 +12923,7 @@
         <v>1.2333333333333335E-3</v>
       </c>
     </row>
-    <row r="442" spans="1:7" x14ac:dyDescent="0.25">
+    <row r="442" spans="1:7" hidden="1" x14ac:dyDescent="0.25">
       <c r="A442">
         <v>445</v>
       </c>
@@ -12837,7 +12946,7 @@
         <v>2.5000000000000001E-3</v>
       </c>
     </row>
-    <row r="443" spans="1:7" x14ac:dyDescent="0.25">
+    <row r="443" spans="1:7" hidden="1" x14ac:dyDescent="0.25">
       <c r="A443">
         <v>446</v>
       </c>
@@ -12860,7 +12969,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="444" spans="1:7" x14ac:dyDescent="0.25">
+    <row r="444" spans="1:7" hidden="1" x14ac:dyDescent="0.25">
       <c r="A444">
         <v>447</v>
       </c>
@@ -12883,7 +12992,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="445" spans="1:7" x14ac:dyDescent="0.25">
+    <row r="445" spans="1:7" hidden="1" x14ac:dyDescent="0.25">
       <c r="A445">
         <v>448</v>
       </c>
@@ -12906,7 +13015,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="446" spans="1:7" x14ac:dyDescent="0.25">
+    <row r="446" spans="1:7" hidden="1" x14ac:dyDescent="0.25">
       <c r="A446">
         <v>449</v>
       </c>
@@ -12929,7 +13038,7 @@
         <v>3.0733333333333328E-2</v>
       </c>
     </row>
-    <row r="447" spans="1:7" x14ac:dyDescent="0.25">
+    <row r="447" spans="1:7" hidden="1" x14ac:dyDescent="0.25">
       <c r="A447">
         <v>450</v>
       </c>
@@ -12952,7 +13061,7 @@
         <v>2.731666666666667E-2</v>
       </c>
     </row>
-    <row r="448" spans="1:7" x14ac:dyDescent="0.25">
+    <row r="448" spans="1:7" hidden="1" x14ac:dyDescent="0.25">
       <c r="A448">
         <v>451</v>
       </c>
@@ -12975,7 +13084,7 @@
         <v>1.7233333333333333E-2</v>
       </c>
     </row>
-    <row r="449" spans="1:7" x14ac:dyDescent="0.25">
+    <row r="449" spans="1:7" hidden="1" x14ac:dyDescent="0.25">
       <c r="A449">
         <v>452</v>
       </c>
@@ -12998,7 +13107,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="450" spans="1:7" x14ac:dyDescent="0.25">
+    <row r="450" spans="1:7" hidden="1" x14ac:dyDescent="0.25">
       <c r="A450">
         <v>453</v>
       </c>
@@ -13021,7 +13130,7 @@
         <v>1.891E-2</v>
       </c>
     </row>
-    <row r="451" spans="1:7" x14ac:dyDescent="0.25">
+    <row r="451" spans="1:7" hidden="1" x14ac:dyDescent="0.25">
       <c r="A451">
         <v>454</v>
       </c>
@@ -13067,7 +13176,7 @@
         <v>2.9580000000000002E-2</v>
       </c>
     </row>
-    <row r="453" spans="1:7" x14ac:dyDescent="0.25">
+    <row r="453" spans="1:7" hidden="1" x14ac:dyDescent="0.25">
       <c r="A453">
         <v>456</v>
       </c>
@@ -13090,7 +13199,7 @@
         <v>1.78E-2</v>
       </c>
     </row>
-    <row r="454" spans="1:7" x14ac:dyDescent="0.25">
+    <row r="454" spans="1:7" hidden="1" x14ac:dyDescent="0.25">
       <c r="A454">
         <v>457</v>
       </c>
@@ -13113,7 +13222,7 @@
         <v>7.2496666666666668E-2</v>
       </c>
     </row>
-    <row r="455" spans="1:7" x14ac:dyDescent="0.25">
+    <row r="455" spans="1:7" hidden="1" x14ac:dyDescent="0.25">
       <c r="A455">
         <v>458</v>
       </c>
@@ -13136,7 +13245,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="456" spans="1:7" x14ac:dyDescent="0.25">
+    <row r="456" spans="1:7" hidden="1" x14ac:dyDescent="0.25">
       <c r="A456">
         <v>459</v>
       </c>
@@ -13159,7 +13268,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="457" spans="1:7" x14ac:dyDescent="0.25">
+    <row r="457" spans="1:7" hidden="1" x14ac:dyDescent="0.25">
       <c r="A457">
         <v>460</v>
       </c>
@@ -13182,7 +13291,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="458" spans="1:7" x14ac:dyDescent="0.25">
+    <row r="458" spans="1:7" hidden="1" x14ac:dyDescent="0.25">
       <c r="A458">
         <v>461</v>
       </c>
@@ -13205,7 +13314,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="459" spans="1:7" x14ac:dyDescent="0.25">
+    <row r="459" spans="1:7" hidden="1" x14ac:dyDescent="0.25">
       <c r="A459">
         <v>462</v>
       </c>
@@ -13228,7 +13337,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="460" spans="1:7" x14ac:dyDescent="0.25">
+    <row r="460" spans="1:7" hidden="1" x14ac:dyDescent="0.25">
       <c r="A460">
         <v>463</v>
       </c>
@@ -13251,7 +13360,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="461" spans="1:7" x14ac:dyDescent="0.25">
+    <row r="461" spans="1:7" hidden="1" x14ac:dyDescent="0.25">
       <c r="A461">
         <v>464</v>
       </c>
@@ -13412,7 +13521,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="468" spans="1:7" x14ac:dyDescent="0.25">
+    <row r="468" spans="1:7" hidden="1" x14ac:dyDescent="0.25">
       <c r="A468">
         <v>471</v>
       </c>
@@ -13435,7 +13544,7 @@
         <v>7.3190000000000005E-2</v>
       </c>
     </row>
-    <row r="469" spans="1:7" x14ac:dyDescent="0.25">
+    <row r="469" spans="1:7" hidden="1" x14ac:dyDescent="0.25">
       <c r="A469">
         <v>472</v>
       </c>
@@ -13458,7 +13567,7 @@
         <v>3.15E-2</v>
       </c>
     </row>
-    <row r="470" spans="1:7" x14ac:dyDescent="0.25">
+    <row r="470" spans="1:7" hidden="1" x14ac:dyDescent="0.25">
       <c r="A470">
         <v>473</v>
       </c>
@@ -13481,7 +13590,7 @@
         <v>2.5499999999999998E-2</v>
       </c>
     </row>
-    <row r="471" spans="1:7" x14ac:dyDescent="0.25">
+    <row r="471" spans="1:7" hidden="1" x14ac:dyDescent="0.25">
       <c r="A471">
         <v>474</v>
       </c>
@@ -13504,7 +13613,7 @@
         <v>5.5833333333333325E-3</v>
       </c>
     </row>
-    <row r="472" spans="1:7" x14ac:dyDescent="0.25">
+    <row r="472" spans="1:7" hidden="1" x14ac:dyDescent="0.25">
       <c r="A472">
         <v>475</v>
       </c>
@@ -13527,7 +13636,7 @@
         <v>9.7633333333333322E-3</v>
       </c>
     </row>
-    <row r="473" spans="1:7" x14ac:dyDescent="0.25">
+    <row r="473" spans="1:7" hidden="1" x14ac:dyDescent="0.25">
       <c r="A473">
         <v>476</v>
       </c>
@@ -13550,7 +13659,7 @@
         <v>3.3933333333333329E-2</v>
       </c>
     </row>
-    <row r="474" spans="1:7" x14ac:dyDescent="0.25">
+    <row r="474" spans="1:7" hidden="1" x14ac:dyDescent="0.25">
       <c r="A474">
         <v>477</v>
       </c>
@@ -13573,7 +13682,7 @@
         <v>1.1200000000000002E-2</v>
       </c>
     </row>
-    <row r="475" spans="1:7" x14ac:dyDescent="0.25">
+    <row r="475" spans="1:7" hidden="1" x14ac:dyDescent="0.25">
       <c r="A475">
         <v>478</v>
       </c>
@@ -13596,7 +13705,7 @@
         <v>0.19041</v>
       </c>
     </row>
-    <row r="476" spans="1:7" x14ac:dyDescent="0.25">
+    <row r="476" spans="1:7" hidden="1" x14ac:dyDescent="0.25">
       <c r="A476">
         <v>479</v>
       </c>
@@ -13619,7 +13728,7 @@
         <v>2.9826666666666668E-2</v>
       </c>
     </row>
-    <row r="477" spans="1:7" x14ac:dyDescent="0.25">
+    <row r="477" spans="1:7" hidden="1" x14ac:dyDescent="0.25">
       <c r="A477">
         <v>480</v>
       </c>
@@ -13642,7 +13751,7 @@
         <v>3.0133333333333331E-2</v>
       </c>
     </row>
-    <row r="478" spans="1:7" x14ac:dyDescent="0.25">
+    <row r="478" spans="1:7" hidden="1" x14ac:dyDescent="0.25">
       <c r="A478">
         <v>481</v>
       </c>
@@ -13665,7 +13774,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="479" spans="1:7" x14ac:dyDescent="0.25">
+    <row r="479" spans="1:7" hidden="1" x14ac:dyDescent="0.25">
       <c r="A479">
         <v>482</v>
       </c>
@@ -13688,7 +13797,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="480" spans="1:7" x14ac:dyDescent="0.25">
+    <row r="480" spans="1:7" hidden="1" x14ac:dyDescent="0.25">
       <c r="A480">
         <v>483</v>
       </c>
@@ -13711,7 +13820,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="481" spans="1:7" x14ac:dyDescent="0.25">
+    <row r="481" spans="1:7" hidden="1" x14ac:dyDescent="0.25">
       <c r="A481">
         <v>484</v>
       </c>
@@ -13734,7 +13843,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="482" spans="1:7" x14ac:dyDescent="0.25">
+    <row r="482" spans="1:7" hidden="1" x14ac:dyDescent="0.25">
       <c r="A482">
         <v>485</v>
       </c>
@@ -13757,7 +13866,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="483" spans="1:7" x14ac:dyDescent="0.25">
+    <row r="483" spans="1:7" hidden="1" x14ac:dyDescent="0.25">
       <c r="A483">
         <v>486</v>
       </c>
@@ -13780,7 +13889,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="484" spans="1:7" x14ac:dyDescent="0.25">
+    <row r="484" spans="1:7" hidden="1" x14ac:dyDescent="0.25">
       <c r="A484">
         <v>487</v>
       </c>
@@ -13803,7 +13912,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="485" spans="1:7" x14ac:dyDescent="0.25">
+    <row r="485" spans="1:7" hidden="1" x14ac:dyDescent="0.25">
       <c r="A485">
         <v>488</v>
       </c>
@@ -13826,7 +13935,7 @@
         <v>7.8000000000000005E-3</v>
       </c>
     </row>
-    <row r="486" spans="1:7" x14ac:dyDescent="0.25">
+    <row r="486" spans="1:7" hidden="1" x14ac:dyDescent="0.25">
       <c r="A486">
         <v>489</v>
       </c>
@@ -13872,7 +13981,7 @@
         <v>1.4216666666666669E-2</v>
       </c>
     </row>
-    <row r="488" spans="1:7" x14ac:dyDescent="0.25">
+    <row r="488" spans="1:7" hidden="1" x14ac:dyDescent="0.25">
       <c r="A488">
         <v>491</v>
       </c>
@@ -13895,7 +14004,7 @@
         <v>1.0166666666666666E-2</v>
       </c>
     </row>
-    <row r="489" spans="1:7" x14ac:dyDescent="0.25">
+    <row r="489" spans="1:7" hidden="1" x14ac:dyDescent="0.25">
       <c r="A489">
         <v>492</v>
       </c>
@@ -13918,7 +14027,7 @@
         <v>1.9199999999999998E-2</v>
       </c>
     </row>
-    <row r="490" spans="1:7" x14ac:dyDescent="0.25">
+    <row r="490" spans="1:7" hidden="1" x14ac:dyDescent="0.25">
       <c r="A490">
         <v>493</v>
       </c>
@@ -13941,7 +14050,7 @@
         <v>2.5633333333333331E-2</v>
       </c>
     </row>
-    <row r="491" spans="1:7" x14ac:dyDescent="0.25">
+    <row r="491" spans="1:7" hidden="1" x14ac:dyDescent="0.25">
       <c r="A491">
         <v>494</v>
       </c>
@@ -13964,7 +14073,7 @@
         <v>1.5933333333333334E-2</v>
       </c>
     </row>
-    <row r="492" spans="1:7" x14ac:dyDescent="0.25">
+    <row r="492" spans="1:7" hidden="1" x14ac:dyDescent="0.25">
       <c r="A492">
         <v>495</v>
       </c>
@@ -13987,7 +14096,7 @@
         <v>3.356E-2</v>
       </c>
     </row>
-    <row r="493" spans="1:7" x14ac:dyDescent="0.25">
+    <row r="493" spans="1:7" hidden="1" x14ac:dyDescent="0.25">
       <c r="A493">
         <v>496</v>
       </c>
@@ -14010,7 +14119,7 @@
         <v>0.156033333333333</v>
       </c>
     </row>
-    <row r="494" spans="1:7" x14ac:dyDescent="0.25">
+    <row r="494" spans="1:7" hidden="1" x14ac:dyDescent="0.25">
       <c r="A494">
         <v>497</v>
       </c>
@@ -14033,7 +14142,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="495" spans="1:7" x14ac:dyDescent="0.25">
+    <row r="495" spans="1:7" hidden="1" x14ac:dyDescent="0.25">
       <c r="A495">
         <v>498</v>
       </c>
@@ -14056,7 +14165,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="496" spans="1:7" x14ac:dyDescent="0.25">
+    <row r="496" spans="1:7" hidden="1" x14ac:dyDescent="0.25">
       <c r="A496">
         <v>499</v>
       </c>
@@ -14079,7 +14188,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="497" spans="1:7" x14ac:dyDescent="0.25">
+    <row r="497" spans="1:7" hidden="1" x14ac:dyDescent="0.25">
       <c r="A497">
         <v>500</v>
       </c>
@@ -14102,7 +14211,7 @@
         <v>3.2373333333333337E-2</v>
       </c>
     </row>
-    <row r="498" spans="1:7" x14ac:dyDescent="0.25">
+    <row r="498" spans="1:7" hidden="1" x14ac:dyDescent="0.25">
       <c r="A498">
         <v>501</v>
       </c>
@@ -14125,7 +14234,7 @@
         <v>7.3666666666666672E-3</v>
       </c>
     </row>
-    <row r="499" spans="1:7" x14ac:dyDescent="0.25">
+    <row r="499" spans="1:7" hidden="1" x14ac:dyDescent="0.25">
       <c r="A499">
         <v>502</v>
       </c>
@@ -14148,7 +14257,7 @@
         <v>2.3666666666666667E-3</v>
       </c>
     </row>
-    <row r="500" spans="1:7" x14ac:dyDescent="0.25">
+    <row r="500" spans="1:7" hidden="1" x14ac:dyDescent="0.25">
       <c r="A500">
         <v>503</v>
       </c>
@@ -14171,7 +14280,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="501" spans="1:7" x14ac:dyDescent="0.25">
+    <row r="501" spans="1:7" hidden="1" x14ac:dyDescent="0.25">
       <c r="A501">
         <v>504</v>
       </c>
@@ -14194,7 +14303,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="502" spans="1:7" x14ac:dyDescent="0.25">
+    <row r="502" spans="1:7" hidden="1" x14ac:dyDescent="0.25">
       <c r="A502">
         <v>505</v>
       </c>
@@ -14217,7 +14326,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="503" spans="1:7" x14ac:dyDescent="0.25">
+    <row r="503" spans="1:7" hidden="1" x14ac:dyDescent="0.25">
       <c r="A503">
         <v>506</v>
       </c>
@@ -14240,7 +14349,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="504" spans="1:7" x14ac:dyDescent="0.25">
+    <row r="504" spans="1:7" hidden="1" x14ac:dyDescent="0.25">
       <c r="A504">
         <v>507</v>
       </c>
@@ -14263,7 +14372,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="505" spans="1:7" x14ac:dyDescent="0.25">
+    <row r="505" spans="1:7" hidden="1" x14ac:dyDescent="0.25">
       <c r="A505">
         <v>508</v>
       </c>
@@ -14286,7 +14395,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="506" spans="1:7" x14ac:dyDescent="0.25">
+    <row r="506" spans="1:7" hidden="1" x14ac:dyDescent="0.25">
       <c r="A506">
         <v>509</v>
       </c>
@@ -14309,7 +14418,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="507" spans="1:7" x14ac:dyDescent="0.25">
+    <row r="507" spans="1:7" hidden="1" x14ac:dyDescent="0.25">
       <c r="A507">
         <v>510</v>
       </c>
@@ -14332,7 +14441,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="508" spans="1:7" x14ac:dyDescent="0.25">
+    <row r="508" spans="1:7" hidden="1" x14ac:dyDescent="0.25">
       <c r="A508">
         <v>511</v>
       </c>
@@ -14355,7 +14464,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="509" spans="1:7" x14ac:dyDescent="0.25">
+    <row r="509" spans="1:7" hidden="1" x14ac:dyDescent="0.25">
       <c r="A509">
         <v>512</v>
       </c>
@@ -14378,7 +14487,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="510" spans="1:7" x14ac:dyDescent="0.25">
+    <row r="510" spans="1:7" hidden="1" x14ac:dyDescent="0.25">
       <c r="A510">
         <v>513</v>
       </c>
@@ -14401,7 +14510,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="511" spans="1:7" x14ac:dyDescent="0.25">
+    <row r="511" spans="1:7" hidden="1" x14ac:dyDescent="0.25">
       <c r="A511">
         <v>514</v>
       </c>
@@ -14424,7 +14533,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="512" spans="1:7" x14ac:dyDescent="0.25">
+    <row r="512" spans="1:7" hidden="1" x14ac:dyDescent="0.25">
       <c r="A512">
         <v>515</v>
       </c>
@@ -14447,7 +14556,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="513" spans="1:7" x14ac:dyDescent="0.25">
+    <row r="513" spans="1:7" hidden="1" x14ac:dyDescent="0.25">
       <c r="A513">
         <v>516</v>
       </c>
@@ -14470,7 +14579,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="514" spans="1:7" x14ac:dyDescent="0.25">
+    <row r="514" spans="1:7" hidden="1" x14ac:dyDescent="0.25">
       <c r="A514">
         <v>517</v>
       </c>
@@ -14493,7 +14602,7 @@
         <v>4.253333333333334E-2</v>
       </c>
     </row>
-    <row r="515" spans="1:7" x14ac:dyDescent="0.25">
+    <row r="515" spans="1:7" hidden="1" x14ac:dyDescent="0.25">
       <c r="A515">
         <v>518</v>
       </c>
@@ -14516,7 +14625,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="516" spans="1:7" x14ac:dyDescent="0.25">
+    <row r="516" spans="1:7" hidden="1" x14ac:dyDescent="0.25">
       <c r="A516">
         <v>519</v>
       </c>
@@ -14539,7 +14648,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="517" spans="1:7" x14ac:dyDescent="0.25">
+    <row r="517" spans="1:7" hidden="1" x14ac:dyDescent="0.25">
       <c r="A517">
         <v>520</v>
       </c>
@@ -14562,7 +14671,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="518" spans="1:7" x14ac:dyDescent="0.25">
+    <row r="518" spans="1:7" hidden="1" x14ac:dyDescent="0.25">
       <c r="A518">
         <v>521</v>
       </c>
@@ -14585,7 +14694,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="519" spans="1:7" x14ac:dyDescent="0.25">
+    <row r="519" spans="1:7" hidden="1" x14ac:dyDescent="0.25">
       <c r="A519">
         <v>522</v>
       </c>
@@ -14608,7 +14717,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="520" spans="1:7" x14ac:dyDescent="0.25">
+    <row r="520" spans="1:7" hidden="1" x14ac:dyDescent="0.25">
       <c r="A520">
         <v>523</v>
       </c>
@@ -14631,7 +14740,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="521" spans="1:7" x14ac:dyDescent="0.25">
+    <row r="521" spans="1:7" hidden="1" x14ac:dyDescent="0.25">
       <c r="A521">
         <v>524</v>
       </c>
@@ -14654,7 +14763,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="522" spans="1:7" x14ac:dyDescent="0.25">
+    <row r="522" spans="1:7" hidden="1" x14ac:dyDescent="0.25">
       <c r="A522">
         <v>525</v>
       </c>
@@ -14677,7 +14786,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="523" spans="1:7" x14ac:dyDescent="0.25">
+    <row r="523" spans="1:7" hidden="1" x14ac:dyDescent="0.25">
       <c r="A523">
         <v>526</v>
       </c>
@@ -14700,7 +14809,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="524" spans="1:7" x14ac:dyDescent="0.25">
+    <row r="524" spans="1:7" hidden="1" x14ac:dyDescent="0.25">
       <c r="A524">
         <v>527</v>
       </c>
@@ -14723,7 +14832,7 @@
         <v>4.5533333333333335E-2</v>
       </c>
     </row>
-    <row r="525" spans="1:7" x14ac:dyDescent="0.25">
+    <row r="525" spans="1:7" hidden="1" x14ac:dyDescent="0.25">
       <c r="A525">
         <v>528</v>
       </c>
@@ -14746,7 +14855,7 @@
         <v>1.8966666666666666E-2</v>
       </c>
     </row>
-    <row r="526" spans="1:7" x14ac:dyDescent="0.25">
+    <row r="526" spans="1:7" hidden="1" x14ac:dyDescent="0.25">
       <c r="A526">
         <v>529</v>
       </c>
@@ -14769,7 +14878,7 @@
         <v>1.6466666666666664E-2</v>
       </c>
     </row>
-    <row r="527" spans="1:7" x14ac:dyDescent="0.25">
+    <row r="527" spans="1:7" hidden="1" x14ac:dyDescent="0.25">
       <c r="A527">
         <v>530</v>
       </c>
@@ -14792,7 +14901,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="528" spans="1:7" x14ac:dyDescent="0.25">
+    <row r="528" spans="1:7" hidden="1" x14ac:dyDescent="0.25">
       <c r="A528">
         <v>531</v>
       </c>
@@ -14815,7 +14924,7 @@
         <v>1.6666666666666666E-2</v>
       </c>
     </row>
-    <row r="529" spans="1:7" x14ac:dyDescent="0.25">
+    <row r="529" spans="1:7" hidden="1" x14ac:dyDescent="0.25">
       <c r="A529">
         <v>532</v>
       </c>
@@ -14838,7 +14947,7 @@
         <v>3.2233333333333329E-2</v>
       </c>
     </row>
-    <row r="530" spans="1:7" x14ac:dyDescent="0.25">
+    <row r="530" spans="1:7" hidden="1" x14ac:dyDescent="0.25">
       <c r="A530">
         <v>533</v>
       </c>
@@ -14861,7 +14970,7 @@
         <v>2.1933333333333332E-2</v>
       </c>
     </row>
-    <row r="531" spans="1:7" x14ac:dyDescent="0.25">
+    <row r="531" spans="1:7" hidden="1" x14ac:dyDescent="0.25">
       <c r="A531">
         <v>534</v>
       </c>
@@ -14884,7 +14993,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="532" spans="1:7" x14ac:dyDescent="0.25">
+    <row r="532" spans="1:7" hidden="1" x14ac:dyDescent="0.25">
       <c r="A532">
         <v>535</v>
       </c>
@@ -14907,7 +15016,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="533" spans="1:7" x14ac:dyDescent="0.25">
+    <row r="533" spans="1:7" hidden="1" x14ac:dyDescent="0.25">
       <c r="A533">
         <v>536</v>
       </c>
@@ -14930,7 +15039,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="534" spans="1:7" x14ac:dyDescent="0.25">
+    <row r="534" spans="1:7" hidden="1" x14ac:dyDescent="0.25">
       <c r="A534">
         <v>537</v>
       </c>
@@ -14953,7 +15062,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="535" spans="1:7" x14ac:dyDescent="0.25">
+    <row r="535" spans="1:7" hidden="1" x14ac:dyDescent="0.25">
       <c r="A535">
         <v>538</v>
       </c>
@@ -14976,7 +15085,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="536" spans="1:7" x14ac:dyDescent="0.25">
+    <row r="536" spans="1:7" hidden="1" x14ac:dyDescent="0.25">
       <c r="A536">
         <v>539</v>
       </c>
@@ -14999,7 +15108,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="537" spans="1:7" x14ac:dyDescent="0.25">
+    <row r="537" spans="1:7" hidden="1" x14ac:dyDescent="0.25">
       <c r="A537">
         <v>540</v>
       </c>
@@ -15022,7 +15131,7 @@
         <v>1.89E-2</v>
       </c>
     </row>
-    <row r="538" spans="1:7" x14ac:dyDescent="0.25">
+    <row r="538" spans="1:7" hidden="1" x14ac:dyDescent="0.25">
       <c r="A538">
         <v>541</v>
       </c>
@@ -15045,7 +15154,7 @@
         <v>1.9733333333333335E-2</v>
       </c>
     </row>
-    <row r="539" spans="1:7" x14ac:dyDescent="0.25">
+    <row r="539" spans="1:7" hidden="1" x14ac:dyDescent="0.25">
       <c r="A539">
         <v>542</v>
       </c>
@@ -15068,7 +15177,7 @@
         <v>1.7500000000000002E-2</v>
       </c>
     </row>
-    <row r="540" spans="1:7" x14ac:dyDescent="0.25">
+    <row r="540" spans="1:7" hidden="1" x14ac:dyDescent="0.25">
       <c r="A540">
         <v>543</v>
       </c>
@@ -15091,7 +15200,7 @@
         <v>4.3866666666666672E-3</v>
       </c>
     </row>
-    <row r="541" spans="1:7" x14ac:dyDescent="0.25">
+    <row r="541" spans="1:7" hidden="1" x14ac:dyDescent="0.25">
       <c r="A541">
         <v>544</v>
       </c>
@@ -15114,7 +15223,7 @@
         <v>1.7399999999999999E-2</v>
       </c>
     </row>
-    <row r="542" spans="1:7" x14ac:dyDescent="0.25">
+    <row r="542" spans="1:7" hidden="1" x14ac:dyDescent="0.25">
       <c r="A542">
         <v>547</v>
       </c>
@@ -15137,7 +15246,7 @@
         <v>2.2166666666666668E-2</v>
       </c>
     </row>
-    <row r="543" spans="1:7" x14ac:dyDescent="0.25">
+    <row r="543" spans="1:7" hidden="1" x14ac:dyDescent="0.25">
       <c r="A543">
         <v>548</v>
       </c>
@@ -15160,7 +15269,7 @@
         <v>2.513333333333333E-2</v>
       </c>
     </row>
-    <row r="544" spans="1:7" x14ac:dyDescent="0.25">
+    <row r="544" spans="1:7" hidden="1" x14ac:dyDescent="0.25">
       <c r="A544">
         <v>549</v>
       </c>
@@ -15183,7 +15292,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="545" spans="1:7" x14ac:dyDescent="0.25">
+    <row r="545" spans="1:7" hidden="1" x14ac:dyDescent="0.25">
       <c r="A545">
         <v>550</v>
       </c>
@@ -15206,7 +15315,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="546" spans="1:7" x14ac:dyDescent="0.25">
+    <row r="546" spans="1:7" hidden="1" x14ac:dyDescent="0.25">
       <c r="A546">
         <v>551</v>
       </c>
@@ -15229,7 +15338,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="547" spans="1:7" x14ac:dyDescent="0.25">
+    <row r="547" spans="1:7" hidden="1" x14ac:dyDescent="0.25">
       <c r="A547">
         <v>552</v>
       </c>
@@ -15252,7 +15361,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="548" spans="1:7" x14ac:dyDescent="0.25">
+    <row r="548" spans="1:7" hidden="1" x14ac:dyDescent="0.25">
       <c r="A548">
         <v>553</v>
       </c>
@@ -15275,7 +15384,7 @@
         <v>4.0999999999999995E-3</v>
       </c>
     </row>
-    <row r="549" spans="1:7" x14ac:dyDescent="0.25">
+    <row r="549" spans="1:7" hidden="1" x14ac:dyDescent="0.25">
       <c r="A549">
         <v>554</v>
       </c>
@@ -15298,7 +15407,7 @@
         <v>1.8500000000000003E-2</v>
       </c>
     </row>
-    <row r="550" spans="1:7" x14ac:dyDescent="0.25">
+    <row r="550" spans="1:7" hidden="1" x14ac:dyDescent="0.25">
       <c r="A550">
         <v>555</v>
       </c>
@@ -15321,7 +15430,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="551" spans="1:7" x14ac:dyDescent="0.25">
+    <row r="551" spans="1:7" hidden="1" x14ac:dyDescent="0.25">
       <c r="A551">
         <v>556</v>
       </c>
@@ -15344,7 +15453,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="552" spans="1:7" x14ac:dyDescent="0.25">
+    <row r="552" spans="1:7" hidden="1" x14ac:dyDescent="0.25">
       <c r="A552">
         <v>557</v>
       </c>
@@ -15367,7 +15476,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="553" spans="1:7" x14ac:dyDescent="0.25">
+    <row r="553" spans="1:7" hidden="1" x14ac:dyDescent="0.25">
       <c r="A553">
         <v>558</v>
       </c>
@@ -15390,7 +15499,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="554" spans="1:7" x14ac:dyDescent="0.25">
+    <row r="554" spans="1:7" hidden="1" x14ac:dyDescent="0.25">
       <c r="A554">
         <v>559</v>
       </c>
@@ -15413,7 +15522,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="555" spans="1:7" x14ac:dyDescent="0.25">
+    <row r="555" spans="1:7" hidden="1" x14ac:dyDescent="0.25">
       <c r="A555">
         <v>560</v>
       </c>
@@ -15436,7 +15545,7 @@
         <v>3.0899999999999997E-2</v>
       </c>
     </row>
-    <row r="556" spans="1:7" x14ac:dyDescent="0.25">
+    <row r="556" spans="1:7" hidden="1" x14ac:dyDescent="0.25">
       <c r="A556">
         <v>561</v>
       </c>
@@ -15459,7 +15568,7 @@
         <v>3.5185000000000001E-2</v>
       </c>
     </row>
-    <row r="557" spans="1:7" x14ac:dyDescent="0.25">
+    <row r="557" spans="1:7" hidden="1" x14ac:dyDescent="0.25">
       <c r="A557">
         <v>562</v>
       </c>
@@ -15482,7 +15591,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="558" spans="1:7" x14ac:dyDescent="0.25">
+    <row r="558" spans="1:7" hidden="1" x14ac:dyDescent="0.25">
       <c r="A558">
         <v>563</v>
       </c>
@@ -15505,7 +15614,7 @@
         <v>3.6633333333333335E-3</v>
       </c>
     </row>
-    <row r="559" spans="1:7" x14ac:dyDescent="0.25">
+    <row r="559" spans="1:7" hidden="1" x14ac:dyDescent="0.25">
       <c r="A559">
         <v>564</v>
       </c>
@@ -15528,7 +15637,7 @@
         <v>7.3130000000000001E-2</v>
       </c>
     </row>
-    <row r="560" spans="1:7" x14ac:dyDescent="0.25">
+    <row r="560" spans="1:7" hidden="1" x14ac:dyDescent="0.25">
       <c r="A560">
         <v>565</v>
       </c>
@@ -15551,7 +15660,7 @@
         <v>0.20180000000000001</v>
       </c>
     </row>
-    <row r="561" spans="1:7" x14ac:dyDescent="0.25">
+    <row r="561" spans="1:7" hidden="1" x14ac:dyDescent="0.25">
       <c r="A561">
         <v>566</v>
       </c>
@@ -15574,7 +15683,7 @@
         <v>7.5266666666666667E-3</v>
       </c>
     </row>
-    <row r="562" spans="1:7" x14ac:dyDescent="0.25">
+    <row r="562" spans="1:7" hidden="1" x14ac:dyDescent="0.25">
       <c r="A562">
         <v>567</v>
       </c>
@@ -15597,7 +15706,7 @@
         <v>2.0833333333333336E-2</v>
       </c>
     </row>
-    <row r="563" spans="1:7" x14ac:dyDescent="0.25">
+    <row r="563" spans="1:7" hidden="1" x14ac:dyDescent="0.25">
       <c r="A563">
         <v>568</v>
       </c>
@@ -15620,7 +15729,7 @@
         <v>2.1333333333333334E-3</v>
       </c>
     </row>
-    <row r="564" spans="1:7" x14ac:dyDescent="0.25">
+    <row r="564" spans="1:7" hidden="1" x14ac:dyDescent="0.25">
       <c r="A564">
         <v>569</v>
       </c>
@@ -15643,7 +15752,7 @@
         <v>4.4536666666666669E-2</v>
       </c>
     </row>
-    <row r="565" spans="1:7" x14ac:dyDescent="0.25">
+    <row r="565" spans="1:7" hidden="1" x14ac:dyDescent="0.25">
       <c r="A565">
         <v>570</v>
       </c>
@@ -15712,7 +15821,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="568" spans="1:7" x14ac:dyDescent="0.25">
+    <row r="568" spans="1:7" hidden="1" x14ac:dyDescent="0.25">
       <c r="A568">
         <v>573</v>
       </c>
@@ -15735,7 +15844,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="569" spans="1:7" x14ac:dyDescent="0.25">
+    <row r="569" spans="1:7" hidden="1" x14ac:dyDescent="0.25">
       <c r="A569">
         <v>574</v>
       </c>
@@ -15758,7 +15867,7 @@
         <v>5.5666666666666677E-3</v>
       </c>
     </row>
-    <row r="570" spans="1:7" x14ac:dyDescent="0.25">
+    <row r="570" spans="1:7" hidden="1" x14ac:dyDescent="0.25">
       <c r="A570">
         <v>575</v>
       </c>
@@ -15781,7 +15890,7 @@
         <v>1.1733333333333332E-2</v>
       </c>
     </row>
-    <row r="571" spans="1:7" x14ac:dyDescent="0.25">
+    <row r="571" spans="1:7" hidden="1" x14ac:dyDescent="0.25">
       <c r="A571">
         <v>576</v>
       </c>
@@ -15804,7 +15913,7 @@
         <v>2.8033299999999997E-2</v>
       </c>
     </row>
-    <row r="572" spans="1:7" x14ac:dyDescent="0.25">
+    <row r="572" spans="1:7" hidden="1" x14ac:dyDescent="0.25">
       <c r="A572">
         <v>577</v>
       </c>
@@ -15827,7 +15936,7 @@
         <v>3.1166666666666665E-2</v>
       </c>
     </row>
-    <row r="573" spans="1:7" x14ac:dyDescent="0.25">
+    <row r="573" spans="1:7" hidden="1" x14ac:dyDescent="0.25">
       <c r="A573">
         <v>578</v>
       </c>
@@ -15850,7 +15959,7 @@
         <v>1.0266666666666667E-2</v>
       </c>
     </row>
-    <row r="574" spans="1:7" x14ac:dyDescent="0.25">
+    <row r="574" spans="1:7" hidden="1" x14ac:dyDescent="0.25">
       <c r="A574">
         <v>579</v>
       </c>
@@ -15873,7 +15982,7 @@
         <v>2.268333333333333E-2</v>
       </c>
     </row>
-    <row r="575" spans="1:7" x14ac:dyDescent="0.25">
+    <row r="575" spans="1:7" hidden="1" x14ac:dyDescent="0.25">
       <c r="A575">
         <v>580</v>
       </c>
@@ -15896,7 +16005,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="576" spans="1:7" x14ac:dyDescent="0.25">
+    <row r="576" spans="1:7" hidden="1" x14ac:dyDescent="0.25">
       <c r="A576">
         <v>581</v>
       </c>
@@ -15919,7 +16028,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="577" spans="1:7" x14ac:dyDescent="0.25">
+    <row r="577" spans="1:7" hidden="1" x14ac:dyDescent="0.25">
       <c r="A577">
         <v>582</v>
       </c>
@@ -15942,7 +16051,7 @@
         <v>0.32306999999999997</v>
       </c>
     </row>
-    <row r="578" spans="1:7" x14ac:dyDescent="0.25">
+    <row r="578" spans="1:7" hidden="1" x14ac:dyDescent="0.25">
       <c r="A578">
         <v>583</v>
       </c>
@@ -15965,7 +16074,7 @@
         <v>0.1444</v>
       </c>
     </row>
-    <row r="579" spans="1:7" x14ac:dyDescent="0.25">
+    <row r="579" spans="1:7" hidden="1" x14ac:dyDescent="0.25">
       <c r="A579">
         <v>584</v>
       </c>
@@ -15988,7 +16097,7 @@
         <v>0.12653333333333333</v>
       </c>
     </row>
-    <row r="580" spans="1:7" x14ac:dyDescent="0.25">
+    <row r="580" spans="1:7" hidden="1" x14ac:dyDescent="0.25">
       <c r="A580">
         <v>585</v>
       </c>
@@ -16011,7 +16120,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="581" spans="1:7" x14ac:dyDescent="0.25">
+    <row r="581" spans="1:7" hidden="1" x14ac:dyDescent="0.25">
       <c r="A581">
         <v>586</v>
       </c>
@@ -16034,7 +16143,7 @@
         <v>2.2666666666666668E-3</v>
       </c>
     </row>
-    <row r="582" spans="1:7" x14ac:dyDescent="0.25">
+    <row r="582" spans="1:7" hidden="1" x14ac:dyDescent="0.25">
       <c r="A582">
         <v>587</v>
       </c>
@@ -16057,7 +16166,7 @@
         <v>1.9820000000000001E-2</v>
       </c>
     </row>
-    <row r="583" spans="1:7" x14ac:dyDescent="0.25">
+    <row r="583" spans="1:7" hidden="1" x14ac:dyDescent="0.25">
       <c r="A583">
         <v>588</v>
       </c>
@@ -16080,7 +16189,7 @@
         <v>1.3363333333333333E-2</v>
       </c>
     </row>
-    <row r="584" spans="1:7" x14ac:dyDescent="0.25">
+    <row r="584" spans="1:7" hidden="1" x14ac:dyDescent="0.25">
       <c r="A584">
         <v>589</v>
       </c>
@@ -16103,7 +16212,7 @@
         <v>9.1999999999999998E-3</v>
       </c>
     </row>
-    <row r="585" spans="1:7" x14ac:dyDescent="0.25">
+    <row r="585" spans="1:7" hidden="1" x14ac:dyDescent="0.25">
       <c r="A585">
         <v>590</v>
       </c>
@@ -16126,7 +16235,7 @@
         <v>9.336666666666665E-3</v>
       </c>
     </row>
-    <row r="586" spans="1:7" x14ac:dyDescent="0.25">
+    <row r="586" spans="1:7" hidden="1" x14ac:dyDescent="0.25">
       <c r="A586">
         <v>591</v>
       </c>
@@ -16149,7 +16258,7 @@
         <v>2.3333333333333331E-3</v>
       </c>
     </row>
-    <row r="587" spans="1:7" x14ac:dyDescent="0.25">
+    <row r="587" spans="1:7" hidden="1" x14ac:dyDescent="0.25">
       <c r="A587">
         <v>592</v>
       </c>
@@ -16172,7 +16281,7 @@
         <v>2.3433333333333334E-2</v>
       </c>
     </row>
-    <row r="588" spans="1:7" x14ac:dyDescent="0.25">
+    <row r="588" spans="1:7" hidden="1" x14ac:dyDescent="0.25">
       <c r="A588">
         <v>593</v>
       </c>
@@ -16195,7 +16304,7 @@
         <v>2.3833333333333331E-2</v>
       </c>
     </row>
-    <row r="589" spans="1:7" x14ac:dyDescent="0.25">
+    <row r="589" spans="1:7" hidden="1" x14ac:dyDescent="0.25">
       <c r="A589">
         <v>594</v>
       </c>
@@ -16218,7 +16327,7 @@
         <v>1.6966666666666665E-2</v>
       </c>
     </row>
-    <row r="590" spans="1:7" x14ac:dyDescent="0.25">
+    <row r="590" spans="1:7" hidden="1" x14ac:dyDescent="0.25">
       <c r="A590">
         <v>595</v>
       </c>
@@ -16241,7 +16350,7 @@
         <v>2.1633333333333334E-2</v>
       </c>
     </row>
-    <row r="591" spans="1:7" x14ac:dyDescent="0.25">
+    <row r="591" spans="1:7" hidden="1" x14ac:dyDescent="0.25">
       <c r="A591">
         <v>596</v>
       </c>
@@ -16262,6 +16371,851 @@
       </c>
       <c r="G591">
         <v>1.0566666666666667E-2</v>
+      </c>
+    </row>
+  </sheetData>
+  <autoFilter ref="A1:G591" xr:uid="{00000000-0001-0000-0000-000000000000}">
+    <filterColumn colId="0">
+      <filters>
+        <filter val="106"/>
+        <filter val="123"/>
+        <filter val="124"/>
+        <filter val="125"/>
+        <filter val="126"/>
+        <filter val="127"/>
+        <filter val="128"/>
+        <filter val="129"/>
+        <filter val="130"/>
+        <filter val="159"/>
+        <filter val="352"/>
+        <filter val="353"/>
+        <filter val="354"/>
+        <filter val="355"/>
+        <filter val="375"/>
+        <filter val="379"/>
+        <filter val="380"/>
+        <filter val="381"/>
+        <filter val="382"/>
+        <filter val="383"/>
+        <filter val="384"/>
+        <filter val="385"/>
+        <filter val="386"/>
+        <filter val="387"/>
+        <filter val="388"/>
+        <filter val="410"/>
+        <filter val="411"/>
+        <filter val="415"/>
+        <filter val="416"/>
+        <filter val="421"/>
+        <filter val="422"/>
+        <filter val="424"/>
+        <filter val="431"/>
+        <filter val="455"/>
+        <filter val="465"/>
+        <filter val="466"/>
+        <filter val="467"/>
+        <filter val="468"/>
+        <filter val="469"/>
+        <filter val="470"/>
+        <filter val="490"/>
+        <filter val="571"/>
+        <filter val="572"/>
+        <filter val="66"/>
+      </filters>
+    </filterColumn>
+  </autoFilter>
+  <pageMargins left="0.511811024" right="0.511811024" top="0.78740157499999996" bottom="0.78740157499999996" header="0.31496062000000002" footer="0.31496062000000002"/>
+</worksheet>
+</file>
+
+<file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{71529505-D6DF-4604-8E68-370EA8439418}">
+  <dimension ref="A1:G34"/>
+  <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
+  <cols>
+    <col min="3" max="3" width="12.5703125" bestFit="1" customWidth="1"/>
+  </cols>
+  <sheetData>
+    <row r="1" spans="1:7" x14ac:dyDescent="0.25">
+      <c r="A1" t="s">
+        <v>745</v>
+      </c>
+      <c r="B1" t="s">
+        <v>611</v>
+      </c>
+      <c r="C1" t="s">
+        <v>746</v>
+      </c>
+      <c r="D1" t="s">
+        <v>747</v>
+      </c>
+      <c r="E1" t="s">
+        <v>748</v>
+      </c>
+      <c r="F1" t="s">
+        <v>749</v>
+      </c>
+      <c r="G1" t="s">
+        <v>750</v>
+      </c>
+    </row>
+    <row r="2" spans="1:7" x14ac:dyDescent="0.25">
+      <c r="A2">
+        <v>66</v>
+      </c>
+      <c r="B2" t="s">
+        <v>179</v>
+      </c>
+      <c r="C2" s="3">
+        <v>14423</v>
+      </c>
+      <c r="D2">
+        <v>1.8599999999999998E-2</v>
+      </c>
+      <c r="E2">
+        <v>0.126</v>
+      </c>
+      <c r="F2">
+        <v>9.0499999999999997E-2</v>
+      </c>
+      <c r="G2">
+        <v>9.4700000000000006E-2</v>
+      </c>
+    </row>
+    <row r="3" spans="1:7" x14ac:dyDescent="0.25">
+      <c r="A3">
+        <v>106</v>
+      </c>
+      <c r="B3" t="s">
+        <v>188</v>
+      </c>
+      <c r="C3" s="3">
+        <v>0.36780000000000002</v>
+      </c>
+      <c r="D3">
+        <v>5.4000000000000003E-3</v>
+      </c>
+      <c r="E3">
+        <v>0</v>
+      </c>
+      <c r="F3">
+        <v>9.69E-2</v>
+      </c>
+      <c r="G3">
+        <v>1.7000000000000001E-2</v>
+      </c>
+    </row>
+    <row r="4" spans="1:7" x14ac:dyDescent="0.25">
+      <c r="A4">
+        <v>159</v>
+      </c>
+      <c r="B4" t="s">
+        <v>200</v>
+      </c>
+      <c r="C4" s="3">
+        <v>0.36470000000000002</v>
+      </c>
+      <c r="D4">
+        <v>1.0200000000000001E-2</v>
+      </c>
+      <c r="E4">
+        <v>0</v>
+      </c>
+      <c r="F4">
+        <v>9.1499999999999998E-2</v>
+      </c>
+      <c r="G4">
+        <v>2.06E-2</v>
+      </c>
+    </row>
+    <row r="5" spans="1:7" x14ac:dyDescent="0.25">
+      <c r="A5">
+        <v>172</v>
+      </c>
+      <c r="B5" t="s">
+        <v>751</v>
+      </c>
+      <c r="C5" s="3">
+        <v>14270</v>
+      </c>
+      <c r="D5">
+        <v>7.1000000000000004E-3</v>
+      </c>
+      <c r="E5">
+        <v>1.4E-3</v>
+      </c>
+      <c r="F5">
+        <v>0.38650000000000001</v>
+      </c>
+      <c r="G5">
+        <v>0.13039999999999999</v>
+      </c>
+    </row>
+    <row r="6" spans="1:7" x14ac:dyDescent="0.25">
+      <c r="A6">
+        <v>320</v>
+      </c>
+      <c r="B6" t="s">
+        <v>210</v>
+      </c>
+      <c r="C6" s="3">
+        <v>0.2072</v>
+      </c>
+      <c r="D6">
+        <v>4.7999999999999996E-3</v>
+      </c>
+      <c r="E6">
+        <v>8.0000000000000004E-4</v>
+      </c>
+      <c r="F6">
+        <v>5.1200000000000002E-2</v>
+      </c>
+      <c r="G6">
+        <v>8.9999999999999993E-3</v>
+      </c>
+    </row>
+    <row r="7" spans="1:7" x14ac:dyDescent="0.25">
+      <c r="A7">
+        <v>379</v>
+      </c>
+      <c r="B7" t="s">
+        <v>752</v>
+      </c>
+      <c r="C7" s="3">
+        <v>0.5907</v>
+      </c>
+      <c r="D7">
+        <v>1.2699999999999999E-2</v>
+      </c>
+      <c r="E7">
+        <v>1.2999999999999999E-3</v>
+      </c>
+      <c r="F7">
+        <v>0.14910000000000001</v>
+      </c>
+      <c r="G7">
+        <v>1.46E-2</v>
+      </c>
+    </row>
+    <row r="8" spans="1:7" x14ac:dyDescent="0.25">
+      <c r="A8">
+        <v>380</v>
+      </c>
+      <c r="B8" t="s">
+        <v>753</v>
+      </c>
+      <c r="C8" s="3">
+        <v>0.7329</v>
+      </c>
+      <c r="D8">
+        <v>1.2999999999999999E-2</v>
+      </c>
+      <c r="E8">
+        <v>0</v>
+      </c>
+      <c r="F8">
+        <v>0.1739</v>
+      </c>
+      <c r="G8">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="9" spans="1:7" x14ac:dyDescent="0.25">
+      <c r="A9">
+        <v>381</v>
+      </c>
+      <c r="B9" t="s">
+        <v>754</v>
+      </c>
+      <c r="C9" s="3">
+        <v>0.66810000000000003</v>
+      </c>
+      <c r="D9">
+        <v>1.4E-2</v>
+      </c>
+      <c r="E9">
+        <v>2.3999999999999998E-3</v>
+      </c>
+      <c r="F9">
+        <v>0.16719999999999999</v>
+      </c>
+      <c r="G9">
+        <v>5.1700000000000003E-2</v>
+      </c>
+    </row>
+    <row r="10" spans="1:7" x14ac:dyDescent="0.25">
+      <c r="A10">
+        <v>382</v>
+      </c>
+      <c r="B10" t="s">
+        <v>755</v>
+      </c>
+      <c r="C10" s="3">
+        <v>0.81910000000000005</v>
+      </c>
+      <c r="D10">
+        <v>1.3299999999999999E-2</v>
+      </c>
+      <c r="E10">
+        <v>2.8E-3</v>
+      </c>
+      <c r="F10">
+        <v>0.1915</v>
+      </c>
+      <c r="G10">
+        <v>2.06E-2</v>
+      </c>
+    </row>
+    <row r="11" spans="1:7" x14ac:dyDescent="0.25">
+      <c r="A11">
+        <v>383</v>
+      </c>
+      <c r="B11" t="s">
+        <v>756</v>
+      </c>
+      <c r="C11" s="3">
+        <v>0.59409999999999996</v>
+      </c>
+      <c r="D11">
+        <v>1.37E-2</v>
+      </c>
+      <c r="E11">
+        <v>1E-3</v>
+      </c>
+      <c r="F11">
+        <v>0.15</v>
+      </c>
+      <c r="G11">
+        <v>2.3099999999999999E-2</v>
+      </c>
+    </row>
+    <row r="12" spans="1:7" x14ac:dyDescent="0.25">
+      <c r="A12">
+        <v>384</v>
+      </c>
+      <c r="B12" t="s">
+        <v>757</v>
+      </c>
+      <c r="C12" s="3">
+        <v>0.78669999999999995</v>
+      </c>
+      <c r="D12">
+        <v>1.43E-2</v>
+      </c>
+      <c r="E12">
+        <v>2.3999999999999998E-3</v>
+      </c>
+      <c r="F12">
+        <v>0.18329999999999999</v>
+      </c>
+      <c r="G12">
+        <v>8.5000000000000006E-3</v>
+      </c>
+    </row>
+    <row r="13" spans="1:7" x14ac:dyDescent="0.25">
+      <c r="A13">
+        <v>385</v>
+      </c>
+      <c r="B13" t="s">
+        <v>758</v>
+      </c>
+      <c r="C13" s="3">
+        <v>0.47799999999999998</v>
+      </c>
+      <c r="D13">
+        <v>1.3599999999999999E-2</v>
+      </c>
+      <c r="E13">
+        <v>1.6000000000000001E-3</v>
+      </c>
+      <c r="F13">
+        <v>0.1163</v>
+      </c>
+      <c r="G13">
+        <v>0.01</v>
+      </c>
+    </row>
+    <row r="14" spans="1:7" x14ac:dyDescent="0.25">
+      <c r="A14">
+        <v>386</v>
+      </c>
+      <c r="B14" t="s">
+        <v>759</v>
+      </c>
+      <c r="C14" s="3">
+        <v>0.6542</v>
+      </c>
+      <c r="D14">
+        <v>1.4800000000000001E-2</v>
+      </c>
+      <c r="E14">
+        <v>1.5E-3</v>
+      </c>
+      <c r="F14">
+        <v>0.15110000000000001</v>
+      </c>
+      <c r="G14">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="15" spans="1:7" x14ac:dyDescent="0.25">
+      <c r="A15">
+        <v>387</v>
+      </c>
+      <c r="B15" t="s">
+        <v>760</v>
+      </c>
+      <c r="C15" s="3">
+        <v>0.59940000000000004</v>
+      </c>
+      <c r="D15">
+        <v>0.01</v>
+      </c>
+      <c r="E15">
+        <v>2.0999999999999999E-3</v>
+      </c>
+      <c r="F15">
+        <v>0.15240000000000001</v>
+      </c>
+      <c r="G15">
+        <v>2.2499999999999999E-2</v>
+      </c>
+    </row>
+    <row r="16" spans="1:7" x14ac:dyDescent="0.25">
+      <c r="A16">
+        <v>388</v>
+      </c>
+      <c r="B16" t="s">
+        <v>761</v>
+      </c>
+      <c r="C16" s="3">
+        <v>0.72389999999999999</v>
+      </c>
+      <c r="D16">
+        <v>9.7000000000000003E-3</v>
+      </c>
+      <c r="E16">
+        <v>2.5000000000000001E-3</v>
+      </c>
+      <c r="F16">
+        <v>0.1711</v>
+      </c>
+      <c r="G16">
+        <v>8.3999999999999995E-3</v>
+      </c>
+    </row>
+    <row r="17" spans="1:7" x14ac:dyDescent="0.25">
+      <c r="A17">
+        <v>410</v>
+      </c>
+      <c r="B17" t="s">
+        <v>762</v>
+      </c>
+      <c r="C17" s="3">
+        <v>0.81289999999999996</v>
+      </c>
+      <c r="D17">
+        <v>2.8999999999999998E-3</v>
+      </c>
+      <c r="E17">
+        <v>3.2000000000000002E-3</v>
+      </c>
+      <c r="F17">
+        <v>0.21560000000000001</v>
+      </c>
+      <c r="G17">
+        <v>2.63E-2</v>
+      </c>
+    </row>
+    <row r="18" spans="1:7" x14ac:dyDescent="0.25">
+      <c r="A18">
+        <v>411</v>
+      </c>
+      <c r="B18" t="s">
+        <v>763</v>
+      </c>
+      <c r="C18" s="3">
+        <v>0.72099999999999997</v>
+      </c>
+      <c r="D18">
+        <v>3.7000000000000002E-3</v>
+      </c>
+      <c r="E18">
+        <v>0</v>
+      </c>
+      <c r="F18">
+        <v>0.19689999999999999</v>
+      </c>
+      <c r="G18">
+        <v>1.7500000000000002E-2</v>
+      </c>
+    </row>
+    <row r="19" spans="1:7" x14ac:dyDescent="0.25">
+      <c r="A19">
+        <v>415</v>
+      </c>
+      <c r="B19" t="s">
+        <v>764</v>
+      </c>
+      <c r="C19" s="3">
+        <v>11335</v>
+      </c>
+      <c r="D19">
+        <v>2.0400000000000001E-2</v>
+      </c>
+      <c r="E19">
+        <v>3.0000000000000001E-3</v>
+      </c>
+      <c r="F19">
+        <v>0.28889999999999999</v>
+      </c>
+      <c r="G19">
+        <v>4.53E-2</v>
+      </c>
+    </row>
+    <row r="20" spans="1:7" x14ac:dyDescent="0.25">
+      <c r="A20">
+        <v>416</v>
+      </c>
+      <c r="B20" t="s">
+        <v>765</v>
+      </c>
+      <c r="C20" s="3">
+        <v>0.60229999999999995</v>
+      </c>
+      <c r="D20">
+        <v>6.7999999999999996E-3</v>
+      </c>
+      <c r="E20">
+        <v>1.9E-3</v>
+      </c>
+      <c r="F20">
+        <v>0.15659999999999999</v>
+      </c>
+      <c r="G20">
+        <v>1.5599999999999999E-2</v>
+      </c>
+    </row>
+    <row r="21" spans="1:7" x14ac:dyDescent="0.25">
+      <c r="A21">
+        <v>421</v>
+      </c>
+      <c r="B21" t="s">
+        <v>766</v>
+      </c>
+      <c r="C21" s="3">
+        <v>12700</v>
+      </c>
+      <c r="D21">
+        <v>8.2000000000000007E-3</v>
+      </c>
+      <c r="E21">
+        <v>5.1000000000000004E-3</v>
+      </c>
+      <c r="F21">
+        <v>0.33329999999999999</v>
+      </c>
+      <c r="G21">
+        <v>3.1600000000000003E-2</v>
+      </c>
+    </row>
+    <row r="22" spans="1:7" x14ac:dyDescent="0.25">
+      <c r="A22">
+        <v>422</v>
+      </c>
+      <c r="B22" t="s">
+        <v>767</v>
+      </c>
+      <c r="C22" s="3">
+        <v>14497</v>
+      </c>
+      <c r="D22">
+        <v>8.2000000000000007E-3</v>
+      </c>
+      <c r="E22">
+        <v>3.3999999999999998E-3</v>
+      </c>
+      <c r="F22">
+        <v>0.38700000000000001</v>
+      </c>
+      <c r="G22">
+        <v>3.27E-2</v>
+      </c>
+    </row>
+    <row r="23" spans="1:7" x14ac:dyDescent="0.25">
+      <c r="A23">
+        <v>424</v>
+      </c>
+      <c r="B23" t="s">
+        <v>768</v>
+      </c>
+      <c r="C23" s="3">
+        <v>10138</v>
+      </c>
+      <c r="D23">
+        <v>1.7100000000000001E-2</v>
+      </c>
+      <c r="E23">
+        <v>4.4000000000000003E-3</v>
+      </c>
+      <c r="F23">
+        <v>0.25540000000000002</v>
+      </c>
+      <c r="G23">
+        <v>4.1300000000000003E-2</v>
+      </c>
+    </row>
+    <row r="24" spans="1:7" x14ac:dyDescent="0.25">
+      <c r="A24">
+        <v>431</v>
+      </c>
+      <c r="B24" t="s">
+        <v>248</v>
+      </c>
+      <c r="C24" s="3">
+        <v>0.47910000000000003</v>
+      </c>
+      <c r="D24">
+        <v>1.3899999999999999E-2</v>
+      </c>
+      <c r="E24">
+        <v>1.47E-2</v>
+      </c>
+      <c r="F24">
+        <v>8.5800000000000001E-2</v>
+      </c>
+      <c r="G24">
+        <v>8.0000000000000002E-3</v>
+      </c>
+    </row>
+    <row r="25" spans="1:7" x14ac:dyDescent="0.25">
+      <c r="A25">
+        <v>455</v>
+      </c>
+      <c r="B25" t="s">
+        <v>256</v>
+      </c>
+      <c r="C25" s="3">
+        <v>0.12759999999999999</v>
+      </c>
+      <c r="D25">
+        <v>8.9999999999999998E-4</v>
+      </c>
+      <c r="E25">
+        <v>0</v>
+      </c>
+      <c r="F25">
+        <v>3.4599999999999999E-2</v>
+      </c>
+      <c r="G25">
+        <v>8.8999999999999999E-3</v>
+      </c>
+    </row>
+    <row r="26" spans="1:7" x14ac:dyDescent="0.25">
+      <c r="A26">
+        <v>465</v>
+      </c>
+      <c r="B26" t="s">
+        <v>769</v>
+      </c>
+      <c r="C26" s="3">
+        <v>0.1769</v>
+      </c>
+      <c r="D26">
+        <v>1.37E-2</v>
+      </c>
+      <c r="E26">
+        <v>1.2699999999999999E-2</v>
+      </c>
+      <c r="F26">
+        <v>8.0000000000000004E-4</v>
+      </c>
+      <c r="G26">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="27" spans="1:7" x14ac:dyDescent="0.25">
+      <c r="A27">
+        <v>466</v>
+      </c>
+      <c r="B27" t="s">
+        <v>770</v>
+      </c>
+      <c r="C27" s="3">
+        <v>0.17829999999999999</v>
+      </c>
+      <c r="D27">
+        <v>4.0300000000000002E-2</v>
+      </c>
+      <c r="E27">
+        <v>2.9999999999999997E-4</v>
+      </c>
+      <c r="F27">
+        <v>0</v>
+      </c>
+      <c r="G27">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="28" spans="1:7" x14ac:dyDescent="0.25">
+      <c r="A28">
+        <v>467</v>
+      </c>
+      <c r="B28" t="s">
+        <v>771</v>
+      </c>
+      <c r="C28" s="3">
+        <v>0.70530000000000004</v>
+      </c>
+      <c r="D28">
+        <v>3.1800000000000002E-2</v>
+      </c>
+      <c r="E28">
+        <v>6.1499999999999999E-2</v>
+      </c>
+      <c r="F28">
+        <v>3.0999999999999999E-3</v>
+      </c>
+      <c r="G28">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="29" spans="1:7" x14ac:dyDescent="0.25">
+      <c r="A29">
+        <v>468</v>
+      </c>
+      <c r="B29" t="s">
+        <v>772</v>
+      </c>
+      <c r="C29" s="3">
+        <v>0.72850000000000004</v>
+      </c>
+      <c r="D29">
+        <v>6.6500000000000004E-2</v>
+      </c>
+      <c r="E29">
+        <v>4.7399999999999998E-2</v>
+      </c>
+      <c r="F29">
+        <v>3.0999999999999999E-3</v>
+      </c>
+      <c r="G29">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="30" spans="1:7" x14ac:dyDescent="0.25">
+      <c r="A30">
+        <v>469</v>
+      </c>
+      <c r="B30" t="s">
+        <v>773</v>
+      </c>
+      <c r="C30" s="3">
+        <v>0.71560000000000001</v>
+      </c>
+      <c r="D30">
+        <v>6.5199999999999994E-2</v>
+      </c>
+      <c r="E30">
+        <v>4.4499999999999998E-2</v>
+      </c>
+      <c r="F30">
+        <v>8.2000000000000007E-3</v>
+      </c>
+      <c r="G30">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="31" spans="1:7" x14ac:dyDescent="0.25">
+      <c r="A31">
+        <v>470</v>
+      </c>
+      <c r="B31" t="s">
+        <v>774</v>
+      </c>
+      <c r="C31" s="3">
+        <v>1.2009000000000001</v>
+      </c>
+      <c r="D31">
+        <v>7.8100000000000003E-2</v>
+      </c>
+      <c r="E31">
+        <v>9.2899999999999996E-2</v>
+      </c>
+      <c r="F31">
+        <v>6.0000000000000001E-3</v>
+      </c>
+      <c r="G31">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="32" spans="1:7" x14ac:dyDescent="0.25">
+      <c r="A32">
+        <v>490</v>
+      </c>
+      <c r="B32" t="s">
+        <v>775</v>
+      </c>
+      <c r="C32" s="3">
+        <v>0.47220000000000001</v>
+      </c>
+      <c r="D32">
+        <v>1.0699999999999999E-2</v>
+      </c>
+      <c r="E32">
+        <v>0</v>
+      </c>
+      <c r="F32">
+        <v>0.1212</v>
+      </c>
+      <c r="G32">
+        <v>1.8499999999999999E-2</v>
+      </c>
+    </row>
+    <row r="33" spans="1:7" x14ac:dyDescent="0.25">
+      <c r="A33">
+        <v>571</v>
+      </c>
+      <c r="B33" t="s">
+        <v>776</v>
+      </c>
+      <c r="C33" s="3">
+        <v>0.45400000000000001</v>
+      </c>
+      <c r="D33">
+        <v>1.0200000000000001E-2</v>
+      </c>
+      <c r="E33">
+        <v>8.9999999999999998E-4</v>
+      </c>
+      <c r="F33">
+        <v>0.11550000000000001</v>
+      </c>
+      <c r="G33">
+        <v>1.1299999999999999E-2</v>
+      </c>
+    </row>
+    <row r="34" spans="1:7" x14ac:dyDescent="0.25">
+      <c r="A34">
+        <v>572</v>
+      </c>
+      <c r="B34" t="s">
+        <v>777</v>
+      </c>
+      <c r="C34" s="3">
+        <v>0.72219999999999995</v>
+      </c>
+      <c r="D34">
+        <v>1.04E-2</v>
+      </c>
+      <c r="E34">
+        <v>0</v>
+      </c>
+      <c r="F34">
+        <v>0.17599999999999999</v>
+      </c>
+      <c r="G34">
+        <v>0</v>
       </c>
     </row>
   </sheetData>
@@ -16269,7 +17223,7 @@
 </worksheet>
 </file>
 
-<file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
+<file path=xl/worksheets/sheet3.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0100-000000000000}">
   <dimension ref="A1:D131"/>
   <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
